--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>16084</v>
       </c>
       <c r="C2">
-        <v>24627</v>
+        <v>24642</v>
       </c>
       <c r="D2">
-        <v>44680</v>
+        <v>44820</v>
       </c>
       <c r="E2">
-        <v>65559</v>
+        <v>65820</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -405,13 +405,13 @@
         <v>16124</v>
       </c>
       <c r="C3">
-        <v>25195</v>
+        <v>25258</v>
       </c>
       <c r="D3">
-        <v>46254</v>
+        <v>46410</v>
       </c>
       <c r="E3">
-        <v>68293</v>
+        <v>68574</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -422,13 +422,13 @@
         <v>13016</v>
       </c>
       <c r="C4">
-        <v>21093</v>
+        <v>21129</v>
       </c>
       <c r="D4">
-        <v>41515</v>
+        <v>41632</v>
       </c>
       <c r="E4">
-        <v>62870</v>
+        <v>63059</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>13016</v>
       </c>
       <c r="C5">
-        <v>21093</v>
+        <v>21129</v>
       </c>
       <c r="D5">
-        <v>41515</v>
+        <v>41632</v>
       </c>
       <c r="E5">
-        <v>62870</v>
+        <v>63059</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>13016</v>
       </c>
       <c r="C6">
-        <v>21093</v>
+        <v>21129</v>
       </c>
       <c r="D6">
-        <v>41515</v>
+        <v>41632</v>
       </c>
       <c r="E6">
-        <v>62870</v>
+        <v>63059</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>15774</v>
       </c>
       <c r="C7">
-        <v>24453</v>
+        <v>24519</v>
       </c>
       <c r="D7">
-        <v>44963</v>
+        <v>45133</v>
       </c>
       <c r="E7">
-        <v>66528</v>
+        <v>66825</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>15774</v>
       </c>
       <c r="C8">
-        <v>24453</v>
+        <v>24519</v>
       </c>
       <c r="D8">
-        <v>44963</v>
+        <v>45133</v>
       </c>
       <c r="E8">
-        <v>66528</v>
+        <v>66825</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>15433</v>
       </c>
       <c r="C9">
-        <v>23732</v>
+        <v>23800</v>
       </c>
       <c r="D9">
-        <v>43687</v>
+        <v>43869</v>
       </c>
       <c r="E9">
-        <v>64747</v>
+        <v>65058</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>15774</v>
       </c>
       <c r="C10">
-        <v>24453</v>
+        <v>24519</v>
       </c>
       <c r="D10">
-        <v>44963</v>
+        <v>45133</v>
       </c>
       <c r="E10">
-        <v>66528</v>
+        <v>66825</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>15774</v>
       </c>
       <c r="C11">
-        <v>24453</v>
+        <v>24519</v>
       </c>
       <c r="D11">
-        <v>44963</v>
+        <v>45133</v>
       </c>
       <c r="E11">
-        <v>66528</v>
+        <v>66825</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,13 +558,13 @@
         <v>13016</v>
       </c>
       <c r="C12">
-        <v>21093</v>
+        <v>21129</v>
       </c>
       <c r="D12">
-        <v>41515</v>
+        <v>41632</v>
       </c>
       <c r="E12">
-        <v>62870</v>
+        <v>63059</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>16124</v>
       </c>
       <c r="C13">
-        <v>25195</v>
+        <v>25258</v>
       </c>
       <c r="D13">
-        <v>46254</v>
+        <v>46410</v>
       </c>
       <c r="E13">
-        <v>68293</v>
+        <v>68574</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -592,13 +592,13 @@
         <v>13016</v>
       </c>
       <c r="C14">
-        <v>21093</v>
+        <v>21129</v>
       </c>
       <c r="D14">
-        <v>41515</v>
+        <v>41632</v>
       </c>
       <c r="E14">
-        <v>62870</v>
+        <v>63059</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -609,13 +609,13 @@
         <v>15774</v>
       </c>
       <c r="C15">
-        <v>24453</v>
+        <v>24519</v>
       </c>
       <c r="D15">
-        <v>44963</v>
+        <v>45133</v>
       </c>
       <c r="E15">
-        <v>66528</v>
+        <v>66825</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>15718</v>
       </c>
       <c r="C16">
-        <v>23871</v>
+        <v>23886</v>
       </c>
       <c r="D16">
-        <v>43378</v>
+        <v>43529</v>
       </c>
       <c r="E16">
-        <v>63749</v>
+        <v>64025</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,13 +643,13 @@
         <v>13016</v>
       </c>
       <c r="C17">
-        <v>21093</v>
+        <v>21129</v>
       </c>
       <c r="D17">
-        <v>41515</v>
+        <v>41632</v>
       </c>
       <c r="E17">
-        <v>62870</v>
+        <v>63059</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -660,13 +660,13 @@
         <v>16124</v>
       </c>
       <c r="C18">
-        <v>25195</v>
+        <v>25258</v>
       </c>
       <c r="D18">
-        <v>46254</v>
+        <v>46410</v>
       </c>
       <c r="E18">
-        <v>68293</v>
+        <v>68574</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -677,13 +677,13 @@
         <v>15718</v>
       </c>
       <c r="C19">
-        <v>23871</v>
+        <v>23886</v>
       </c>
       <c r="D19">
-        <v>43378</v>
+        <v>43529</v>
       </c>
       <c r="E19">
-        <v>63749</v>
+        <v>64025</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>15718</v>
       </c>
       <c r="C20">
-        <v>23871</v>
+        <v>23886</v>
       </c>
       <c r="D20">
-        <v>43378</v>
+        <v>43529</v>
       </c>
       <c r="E20">
-        <v>63749</v>
+        <v>64025</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>15718</v>
       </c>
       <c r="C21">
-        <v>23871</v>
+        <v>23886</v>
       </c>
       <c r="D21">
-        <v>43378</v>
+        <v>43529</v>
       </c>
       <c r="E21">
-        <v>63749</v>
+        <v>64025</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -728,13 +728,13 @@
         <v>20874</v>
       </c>
       <c r="C22">
-        <v>31304</v>
+        <v>31390</v>
       </c>
       <c r="D22">
-        <v>53068</v>
+        <v>53319</v>
       </c>
       <c r="E22">
-        <v>75130</v>
+        <v>75601</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,13 +745,13 @@
         <v>16084</v>
       </c>
       <c r="C23">
-        <v>24627</v>
+        <v>24642</v>
       </c>
       <c r="D23">
-        <v>44680</v>
+        <v>44820</v>
       </c>
       <c r="E23">
-        <v>65559</v>
+        <v>65820</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -762,13 +762,13 @@
         <v>9966</v>
       </c>
       <c r="C24">
-        <v>16402</v>
+        <v>16404</v>
       </c>
       <c r="D24">
-        <v>34771</v>
+        <v>34813</v>
       </c>
       <c r="E24">
-        <v>53253</v>
+        <v>53332</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>9966</v>
       </c>
       <c r="C25">
-        <v>16402</v>
+        <v>16404</v>
       </c>
       <c r="D25">
-        <v>34771</v>
+        <v>34813</v>
       </c>
       <c r="E25">
-        <v>53253</v>
+        <v>53332</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -796,13 +796,13 @@
         <v>9966</v>
       </c>
       <c r="C26">
-        <v>16402</v>
+        <v>16404</v>
       </c>
       <c r="D26">
-        <v>34771</v>
+        <v>34813</v>
       </c>
       <c r="E26">
-        <v>53253</v>
+        <v>53332</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -816,10 +816,10 @@
         <v>24465</v>
       </c>
       <c r="D27">
-        <v>43459</v>
+        <v>43557</v>
       </c>
       <c r="E27">
-        <v>64221</v>
+        <v>64425</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -833,10 +833,10 @@
         <v>24465</v>
       </c>
       <c r="D28">
-        <v>43459</v>
+        <v>43557</v>
       </c>
       <c r="E28">
-        <v>64221</v>
+        <v>64425</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -850,10 +850,10 @@
         <v>24465</v>
       </c>
       <c r="D29">
-        <v>43459</v>
+        <v>43557</v>
       </c>
       <c r="E29">
-        <v>64221</v>
+        <v>64425</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>26665</v>
       </c>
       <c r="C30">
-        <v>34572</v>
+        <v>34732</v>
       </c>
       <c r="D30">
-        <v>54798</v>
+        <v>55542</v>
       </c>
       <c r="E30">
-        <v>77615</v>
+        <v>78232</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>26665</v>
       </c>
       <c r="C31">
-        <v>34572</v>
+        <v>34732</v>
       </c>
       <c r="D31">
-        <v>54798</v>
+        <v>55542</v>
       </c>
       <c r="E31">
-        <v>77615</v>
+        <v>78232</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>27109</v>
       </c>
       <c r="C32">
-        <v>35454</v>
+        <v>35614</v>
       </c>
       <c r="D32">
-        <v>56104</v>
+        <v>56814</v>
       </c>
       <c r="E32">
-        <v>79065</v>
+        <v>79638</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>26665</v>
       </c>
       <c r="C33">
-        <v>34572</v>
+        <v>34732</v>
       </c>
       <c r="D33">
-        <v>54798</v>
+        <v>55542</v>
       </c>
       <c r="E33">
-        <v>77615</v>
+        <v>78232</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>32601</v>
+        <v>32619</v>
       </c>
       <c r="C34">
-        <v>40802</v>
+        <v>41024</v>
       </c>
       <c r="D34">
-        <v>60928</v>
+        <v>61528</v>
       </c>
       <c r="E34">
-        <v>83380</v>
+        <v>83765</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,13 +949,13 @@
         <v>34057</v>
       </c>
       <c r="C35">
-        <v>42273</v>
+        <v>42376</v>
       </c>
       <c r="D35">
-        <v>62315</v>
+        <v>62906</v>
       </c>
       <c r="E35">
-        <v>84474</v>
+        <v>84860</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -966,13 +966,13 @@
         <v>22297</v>
       </c>
       <c r="C36">
-        <v>30062</v>
+        <v>30174</v>
       </c>
       <c r="D36">
-        <v>51263</v>
+        <v>51829</v>
       </c>
       <c r="E36">
-        <v>75069</v>
+        <v>75673</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>27516</v>
       </c>
       <c r="C37">
-        <v>35436</v>
+        <v>35564</v>
       </c>
       <c r="D37">
-        <v>55369</v>
+        <v>56171</v>
       </c>
       <c r="E37">
-        <v>77959</v>
+        <v>78552</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>27516</v>
       </c>
       <c r="C38">
-        <v>35436</v>
+        <v>35564</v>
       </c>
       <c r="D38">
-        <v>55369</v>
+        <v>56171</v>
       </c>
       <c r="E38">
-        <v>77959</v>
+        <v>78552</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>32146</v>
+        <v>32164</v>
       </c>
       <c r="C39">
-        <v>39973</v>
+        <v>40196</v>
       </c>
       <c r="D39">
-        <v>59700</v>
+        <v>60337</v>
       </c>
       <c r="E39">
-        <v>82069</v>
+        <v>82495</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>34057</v>
       </c>
       <c r="C40">
-        <v>42273</v>
+        <v>42376</v>
       </c>
       <c r="D40">
-        <v>62315</v>
+        <v>62906</v>
       </c>
       <c r="E40">
-        <v>84474</v>
+        <v>84860</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,13 +1051,13 @@
         <v>34057</v>
       </c>
       <c r="C41">
-        <v>42273</v>
+        <v>42376</v>
       </c>
       <c r="D41">
-        <v>62315</v>
+        <v>62906</v>
       </c>
       <c r="E41">
-        <v>84474</v>
+        <v>84860</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1068,13 +1068,13 @@
         <v>24696</v>
       </c>
       <c r="C42">
-        <v>32949</v>
+        <v>33035</v>
       </c>
       <c r="D42">
-        <v>53844</v>
+        <v>54556</v>
       </c>
       <c r="E42">
-        <v>77158</v>
+        <v>77736</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,13 +1085,13 @@
         <v>25168</v>
       </c>
       <c r="C43">
-        <v>33844</v>
+        <v>33930</v>
       </c>
       <c r="D43">
-        <v>55162</v>
+        <v>55838</v>
       </c>
       <c r="E43">
-        <v>78614</v>
+        <v>79145</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1102,13 +1102,13 @@
         <v>24066</v>
       </c>
       <c r="C44">
-        <v>33126</v>
+        <v>33294</v>
       </c>
       <c r="D44">
-        <v>54871</v>
+        <v>55536</v>
       </c>
       <c r="E44">
-        <v>78333</v>
+        <v>78921</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>22042</v>
       </c>
       <c r="C45">
-        <v>29876</v>
+        <v>29903</v>
       </c>
       <c r="D45">
-        <v>50822</v>
+        <v>51375</v>
       </c>
       <c r="E45">
-        <v>74227</v>
+        <v>74770</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>27989</v>
       </c>
       <c r="C46">
-        <v>36332</v>
+        <v>36460</v>
       </c>
       <c r="D46">
-        <v>56660</v>
+        <v>57423</v>
       </c>
       <c r="E46">
-        <v>79398</v>
+        <v>79945</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>22690</v>
       </c>
       <c r="C47">
-        <v>30905</v>
+        <v>31017</v>
       </c>
       <c r="D47">
-        <v>52580</v>
+        <v>53117</v>
       </c>
       <c r="E47">
-        <v>76579</v>
+        <v>77143</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,13 +1170,13 @@
         <v>22471</v>
       </c>
       <c r="C48">
-        <v>30746</v>
+        <v>30773</v>
       </c>
       <c r="D48">
-        <v>52143</v>
+        <v>52672</v>
       </c>
       <c r="E48">
-        <v>75750</v>
+        <v>76255</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1187,13 +1187,13 @@
         <v>18020</v>
       </c>
       <c r="C49">
-        <v>25563</v>
+        <v>25599</v>
       </c>
       <c r="D49">
-        <v>40602</v>
+        <v>40742</v>
       </c>
       <c r="E49">
-        <v>55998</v>
+        <v>56164</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1207,10 +1207,10 @@
         <v>24221</v>
       </c>
       <c r="D50">
-        <v>39913</v>
+        <v>39991</v>
       </c>
       <c r="E50">
-        <v>56454</v>
+        <v>56546</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1221,13 +1221,13 @@
         <v>14154</v>
       </c>
       <c r="C51">
-        <v>21344</v>
+        <v>21365</v>
       </c>
       <c r="D51">
-        <v>36741</v>
+        <v>36851</v>
       </c>
       <c r="E51">
-        <v>51427</v>
+        <v>51519</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1238,13 +1238,13 @@
         <v>15252</v>
       </c>
       <c r="C52">
-        <v>22979</v>
+        <v>23051</v>
       </c>
       <c r="D52">
-        <v>38822</v>
+        <v>38947</v>
       </c>
       <c r="E52">
-        <v>54396</v>
+        <v>54515</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1255,13 +1255,13 @@
         <v>14690</v>
       </c>
       <c r="C53">
-        <v>21694</v>
+        <v>21705</v>
       </c>
       <c r="D53">
-        <v>36937</v>
+        <v>37056</v>
       </c>
       <c r="E53">
-        <v>51824</v>
+        <v>51922</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>13853</v>
       </c>
       <c r="C54">
-        <v>20740</v>
+        <v>20760</v>
       </c>
       <c r="D54">
-        <v>35721</v>
+        <v>35841</v>
       </c>
       <c r="E54">
-        <v>49862</v>
+        <v>49961</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1292,10 +1292,10 @@
         <v>24221</v>
       </c>
       <c r="D55">
-        <v>39913</v>
+        <v>39991</v>
       </c>
       <c r="E55">
-        <v>56454</v>
+        <v>56546</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1306,13 +1306,13 @@
         <v>20584</v>
       </c>
       <c r="C56">
-        <v>28657</v>
+        <v>28714</v>
       </c>
       <c r="D56">
-        <v>44570</v>
+        <v>44695</v>
       </c>
       <c r="E56">
-        <v>61476</v>
+        <v>61682</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1323,13 +1323,13 @@
         <v>13913</v>
       </c>
       <c r="C57">
-        <v>21233</v>
+        <v>21248</v>
       </c>
       <c r="D57">
-        <v>37710</v>
+        <v>37807</v>
       </c>
       <c r="E57">
-        <v>54214</v>
+        <v>54295</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1343,10 +1343,10 @@
         <v>26355</v>
       </c>
       <c r="D58">
-        <v>42928</v>
+        <v>42960</v>
       </c>
       <c r="E58">
-        <v>61668</v>
+        <v>61804</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1360,10 +1360,10 @@
         <v>26355</v>
       </c>
       <c r="D59">
-        <v>42928</v>
+        <v>42960</v>
       </c>
       <c r="E59">
-        <v>61668</v>
+        <v>61804</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1377,10 +1377,10 @@
         <v>16975</v>
       </c>
       <c r="D60">
-        <v>33669</v>
+        <v>33713</v>
       </c>
       <c r="E60">
-        <v>50852</v>
+        <v>50917</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1394,10 +1394,10 @@
         <v>16975</v>
       </c>
       <c r="D61">
-        <v>33669</v>
+        <v>33713</v>
       </c>
       <c r="E61">
-        <v>50852</v>
+        <v>50917</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1411,10 +1411,10 @@
         <v>10558</v>
       </c>
       <c r="D62">
-        <v>28562</v>
+        <v>28579</v>
       </c>
       <c r="E62">
-        <v>47002</v>
+        <v>47041</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1428,10 +1428,10 @@
         <v>10558</v>
       </c>
       <c r="D63">
-        <v>28562</v>
+        <v>28579</v>
       </c>
       <c r="E63">
-        <v>47002</v>
+        <v>47041</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>3937</v>
       </c>
       <c r="C64">
-        <v>8726</v>
+        <v>8730</v>
       </c>
       <c r="D64">
-        <v>26269</v>
+        <v>26282</v>
       </c>
       <c r="E64">
-        <v>43977</v>
+        <v>44007</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>3937</v>
       </c>
       <c r="C65">
-        <v>8726</v>
+        <v>8730</v>
       </c>
       <c r="D65">
-        <v>26269</v>
+        <v>26282</v>
       </c>
       <c r="E65">
-        <v>43977</v>
+        <v>44007</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>17114</v>
       </c>
       <c r="C66">
-        <v>25405</v>
+        <v>25472</v>
       </c>
       <c r="D66">
-        <v>47539</v>
+        <v>47922</v>
       </c>
       <c r="E66">
-        <v>71763</v>
+        <v>72434</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,13 +1493,13 @@
         <v>17496</v>
       </c>
       <c r="C67">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D67">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E67">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1510,13 +1510,13 @@
         <v>17114</v>
       </c>
       <c r="C68">
-        <v>25405</v>
+        <v>25472</v>
       </c>
       <c r="D68">
-        <v>47539</v>
+        <v>47922</v>
       </c>
       <c r="E68">
-        <v>71763</v>
+        <v>72434</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,13 +1527,13 @@
         <v>17496</v>
       </c>
       <c r="C69">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D69">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E69">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1544,13 +1544,13 @@
         <v>17496</v>
       </c>
       <c r="C70">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D70">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E70">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1561,13 +1561,13 @@
         <v>19050</v>
       </c>
       <c r="C71">
-        <v>28481</v>
+        <v>28561</v>
       </c>
       <c r="D71">
-        <v>51916</v>
+        <v>52377</v>
       </c>
       <c r="E71">
-        <v>76534</v>
+        <v>77215</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>17496</v>
       </c>
       <c r="C72">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D72">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E72">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>17496</v>
       </c>
       <c r="C73">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D73">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E73">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>17496</v>
       </c>
       <c r="C74">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D74">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E74">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>12659</v>
       </c>
       <c r="C75">
-        <v>19463</v>
+        <v>19470</v>
       </c>
       <c r="D75">
-        <v>39940</v>
+        <v>40065</v>
       </c>
       <c r="E75">
-        <v>63376</v>
+        <v>63760</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,13 +1646,13 @@
         <v>17496</v>
       </c>
       <c r="C76">
-        <v>26222</v>
+        <v>26286</v>
       </c>
       <c r="D76">
-        <v>48885</v>
+        <v>49248</v>
       </c>
       <c r="E76">
-        <v>73398</v>
+        <v>74026</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1663,13 +1663,13 @@
         <v>16749</v>
       </c>
       <c r="C77">
-        <v>25222</v>
+        <v>25257</v>
       </c>
       <c r="D77">
-        <v>47987</v>
+        <v>48302</v>
       </c>
       <c r="E77">
-        <v>72763</v>
+        <v>73361</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>16749</v>
       </c>
       <c r="C78">
-        <v>25222</v>
+        <v>25257</v>
       </c>
       <c r="D78">
-        <v>47987</v>
+        <v>48302</v>
       </c>
       <c r="E78">
-        <v>72763</v>
+        <v>73361</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>16749</v>
       </c>
       <c r="C79">
-        <v>25222</v>
+        <v>25257</v>
       </c>
       <c r="D79">
-        <v>47987</v>
+        <v>48302</v>
       </c>
       <c r="E79">
-        <v>72763</v>
+        <v>73361</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>16749</v>
       </c>
       <c r="C80">
-        <v>25222</v>
+        <v>25257</v>
       </c>
       <c r="D80">
-        <v>47987</v>
+        <v>48302</v>
       </c>
       <c r="E80">
-        <v>72763</v>
+        <v>73361</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>25116</v>
       </c>
       <c r="C81">
-        <v>33750</v>
+        <v>33852</v>
       </c>
       <c r="D81">
-        <v>54647</v>
+        <v>55236</v>
       </c>
       <c r="E81">
-        <v>77178</v>
+        <v>77770</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>25116</v>
       </c>
       <c r="C82">
-        <v>33750</v>
+        <v>33852</v>
       </c>
       <c r="D82">
-        <v>54647</v>
+        <v>55236</v>
       </c>
       <c r="E82">
-        <v>77178</v>
+        <v>77770</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>16709</v>
       </c>
       <c r="C83">
-        <v>23779</v>
+        <v>23780</v>
       </c>
       <c r="D83">
-        <v>43898</v>
+        <v>44040</v>
       </c>
       <c r="E83">
-        <v>66291</v>
+        <v>66616</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>16709</v>
       </c>
       <c r="C84">
-        <v>23779</v>
+        <v>23780</v>
       </c>
       <c r="D84">
-        <v>43898</v>
+        <v>44040</v>
       </c>
       <c r="E84">
-        <v>66291</v>
+        <v>66616</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>26640</v>
       </c>
       <c r="C85">
-        <v>35349</v>
+        <v>35355</v>
       </c>
       <c r="D85">
-        <v>55398</v>
+        <v>55946</v>
       </c>
       <c r="E85">
-        <v>77290</v>
+        <v>77810</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>26640</v>
       </c>
       <c r="C86">
-        <v>35349</v>
+        <v>35355</v>
       </c>
       <c r="D86">
-        <v>55398</v>
+        <v>55946</v>
       </c>
       <c r="E86">
-        <v>77290</v>
+        <v>77810</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>25597</v>
       </c>
       <c r="C87">
-        <v>34847</v>
+        <v>34939</v>
       </c>
       <c r="D87">
-        <v>56210</v>
+        <v>56815</v>
       </c>
       <c r="E87">
-        <v>78601</v>
+        <v>79155</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>25597</v>
       </c>
       <c r="C88">
-        <v>34847</v>
+        <v>34939</v>
       </c>
       <c r="D88">
-        <v>56210</v>
+        <v>56815</v>
       </c>
       <c r="E88">
-        <v>78601</v>
+        <v>79155</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>25597</v>
       </c>
       <c r="C89">
-        <v>34847</v>
+        <v>34939</v>
       </c>
       <c r="D89">
-        <v>56210</v>
+        <v>56815</v>
       </c>
       <c r="E89">
-        <v>78601</v>
+        <v>79155</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1884,13 +1884,13 @@
         <v>51204</v>
       </c>
       <c r="C90">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D90">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E90">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1901,13 +1901,13 @@
         <v>51204</v>
       </c>
       <c r="C91">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D91">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E91">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1918,13 +1918,13 @@
         <v>51204</v>
       </c>
       <c r="C92">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D92">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E92">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1935,13 +1935,13 @@
         <v>51204</v>
       </c>
       <c r="C93">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D93">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E93">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1949,16 +1949,16 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>52411</v>
+        <v>52419</v>
       </c>
       <c r="C94">
-        <v>61615</v>
+        <v>61725</v>
       </c>
       <c r="D94">
-        <v>78000</v>
+        <v>78243</v>
       </c>
       <c r="E94">
-        <v>94612</v>
+        <v>94696</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1969,13 +1969,13 @@
         <v>51204</v>
       </c>
       <c r="C95">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D95">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E95">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1986,13 +1986,13 @@
         <v>51204</v>
       </c>
       <c r="C96">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D96">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E96">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2003,13 +2003,13 @@
         <v>51204</v>
       </c>
       <c r="C97">
-        <v>59729</v>
+        <v>59800</v>
       </c>
       <c r="D97">
-        <v>76437</v>
+        <v>76661</v>
       </c>
       <c r="E97">
-        <v>93649</v>
+        <v>93744</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2020,13 +2020,13 @@
         <v>49706</v>
       </c>
       <c r="C98">
-        <v>59157</v>
+        <v>59262</v>
       </c>
       <c r="D98">
-        <v>77019</v>
+        <v>77320</v>
       </c>
       <c r="E98">
-        <v>94235</v>
+        <v>94355</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2037,13 +2037,13 @@
         <v>49706</v>
       </c>
       <c r="C99">
-        <v>59157</v>
+        <v>59262</v>
       </c>
       <c r="D99">
-        <v>77019</v>
+        <v>77320</v>
       </c>
       <c r="E99">
-        <v>94235</v>
+        <v>94355</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>50372</v>
       </c>
       <c r="C100">
-        <v>58921</v>
+        <v>58969</v>
       </c>
       <c r="D100">
-        <v>76070</v>
+        <v>76296</v>
       </c>
       <c r="E100">
-        <v>93519</v>
+        <v>93620</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>50372</v>
       </c>
       <c r="C101">
-        <v>58921</v>
+        <v>58969</v>
       </c>
       <c r="D101">
-        <v>76070</v>
+        <v>76296</v>
       </c>
       <c r="E101">
-        <v>93519</v>
+        <v>93620</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>50372</v>
       </c>
       <c r="C102">
-        <v>58921</v>
+        <v>58969</v>
       </c>
       <c r="D102">
-        <v>76070</v>
+        <v>76296</v>
       </c>
       <c r="E102">
-        <v>93519</v>
+        <v>93620</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2105,13 +2105,13 @@
         <v>47395</v>
       </c>
       <c r="C103">
-        <v>57198</v>
+        <v>57379</v>
       </c>
       <c r="D103">
-        <v>75832</v>
+        <v>76211</v>
       </c>
       <c r="E103">
-        <v>93452</v>
+        <v>93607</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2122,13 +2122,13 @@
         <v>47395</v>
       </c>
       <c r="C104">
-        <v>57198</v>
+        <v>57379</v>
       </c>
       <c r="D104">
-        <v>75832</v>
+        <v>76211</v>
       </c>
       <c r="E104">
-        <v>93452</v>
+        <v>93607</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>47837</v>
       </c>
       <c r="C105">
-        <v>57221</v>
+        <v>57243</v>
       </c>
       <c r="D105">
-        <v>75885</v>
+        <v>76111</v>
       </c>
       <c r="E105">
-        <v>93729</v>
+        <v>93847</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2156,13 +2156,13 @@
         <v>48669</v>
       </c>
       <c r="C106">
-        <v>59466</v>
+        <v>59640</v>
       </c>
       <c r="D106">
-        <v>78350</v>
+        <v>78686</v>
       </c>
       <c r="E106">
-        <v>95396</v>
+        <v>95523</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2173,13 +2173,13 @@
         <v>48669</v>
       </c>
       <c r="C107">
-        <v>59466</v>
+        <v>59640</v>
       </c>
       <c r="D107">
-        <v>78350</v>
+        <v>78686</v>
       </c>
       <c r="E107">
-        <v>95396</v>
+        <v>95523</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,13 +2190,13 @@
         <v>49036</v>
       </c>
       <c r="C108">
-        <v>59428</v>
+        <v>59448</v>
       </c>
       <c r="D108">
-        <v>78368</v>
+        <v>78567</v>
       </c>
       <c r="E108">
-        <v>95630</v>
+        <v>95724</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2207,13 +2207,13 @@
         <v>46836</v>
       </c>
       <c r="C109">
-        <v>56552</v>
+        <v>56711</v>
       </c>
       <c r="D109">
-        <v>75136</v>
+        <v>75485</v>
       </c>
       <c r="E109">
-        <v>92891</v>
+        <v>93038</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2224,13 +2224,13 @@
         <v>46836</v>
       </c>
       <c r="C110">
-        <v>56552</v>
+        <v>56711</v>
       </c>
       <c r="D110">
-        <v>75136</v>
+        <v>75485</v>
       </c>
       <c r="E110">
-        <v>92891</v>
+        <v>93038</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2241,13 +2241,13 @@
         <v>46836</v>
       </c>
       <c r="C111">
-        <v>56552</v>
+        <v>56711</v>
       </c>
       <c r="D111">
-        <v>75136</v>
+        <v>75485</v>
       </c>
       <c r="E111">
-        <v>92891</v>
+        <v>93038</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>47955</v>
+        <v>47957</v>
       </c>
       <c r="C112">
-        <v>57961</v>
+        <v>58201</v>
       </c>
       <c r="D112">
-        <v>76419</v>
+        <v>76804</v>
       </c>
       <c r="E112">
-        <v>93788</v>
+        <v>93933</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>45554</v>
       </c>
       <c r="C113">
-        <v>55206</v>
+        <v>55325</v>
       </c>
       <c r="D113">
-        <v>74242</v>
+        <v>74602</v>
       </c>
       <c r="E113">
-        <v>92372</v>
+        <v>92533</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>46185</v>
       </c>
       <c r="C114">
-        <v>56338</v>
+        <v>56454</v>
       </c>
       <c r="D114">
-        <v>75556</v>
+        <v>75896</v>
       </c>
       <c r="E114">
-        <v>93424</v>
+        <v>93570</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>47955</v>
+        <v>47957</v>
       </c>
       <c r="C115">
-        <v>57961</v>
+        <v>58201</v>
       </c>
       <c r="D115">
-        <v>76419</v>
+        <v>76804</v>
       </c>
       <c r="E115">
-        <v>93788</v>
+        <v>93933</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>47955</v>
+        <v>47957</v>
       </c>
       <c r="C116">
-        <v>57961</v>
+        <v>58201</v>
       </c>
       <c r="D116">
-        <v>76419</v>
+        <v>76804</v>
       </c>
       <c r="E116">
-        <v>93788</v>
+        <v>93933</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>45554</v>
       </c>
       <c r="C117">
-        <v>55206</v>
+        <v>55325</v>
       </c>
       <c r="D117">
-        <v>74242</v>
+        <v>74602</v>
       </c>
       <c r="E117">
-        <v>92372</v>
+        <v>92533</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>46833</v>
       </c>
       <c r="C118">
-        <v>57474</v>
+        <v>57589</v>
       </c>
       <c r="D118">
-        <v>76841</v>
+        <v>77157</v>
       </c>
       <c r="E118">
-        <v>94416</v>
+        <v>94548</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,13 +2377,13 @@
         <v>43709</v>
       </c>
       <c r="C119">
-        <v>53078</v>
+        <v>53130</v>
       </c>
       <c r="D119">
-        <v>72245</v>
+        <v>72559</v>
       </c>
       <c r="E119">
-        <v>91019</v>
+        <v>91168</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>50256</v>
+        <v>50257</v>
       </c>
       <c r="C120">
-        <v>59379</v>
+        <v>59490</v>
       </c>
       <c r="D120">
-        <v>76581</v>
+        <v>76866</v>
       </c>
       <c r="E120">
-        <v>93672</v>
+        <v>93783</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>50256</v>
+        <v>50257</v>
       </c>
       <c r="C121">
-        <v>59379</v>
+        <v>59490</v>
       </c>
       <c r="D121">
-        <v>76581</v>
+        <v>76866</v>
       </c>
       <c r="E121">
-        <v>93672</v>
+        <v>93783</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>49026</v>
       </c>
       <c r="C122">
-        <v>58432</v>
+        <v>58546</v>
       </c>
       <c r="D122">
-        <v>75918</v>
+        <v>76196</v>
       </c>
       <c r="E122">
-        <v>93075</v>
+        <v>93199</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>49026</v>
       </c>
       <c r="C123">
-        <v>58432</v>
+        <v>58546</v>
       </c>
       <c r="D123">
-        <v>75918</v>
+        <v>76196</v>
       </c>
       <c r="E123">
-        <v>93075</v>
+        <v>93199</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>49026</v>
       </c>
       <c r="C124">
-        <v>58432</v>
+        <v>58546</v>
       </c>
       <c r="D124">
-        <v>75918</v>
+        <v>76196</v>
       </c>
       <c r="E124">
-        <v>93075</v>
+        <v>93199</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2476,16 +2476,16 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>48716</v>
+        <v>48718</v>
       </c>
       <c r="C125">
-        <v>58427</v>
+        <v>58574</v>
       </c>
       <c r="D125">
-        <v>75684</v>
+        <v>76003</v>
       </c>
       <c r="E125">
-        <v>92462</v>
+        <v>92609</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2493,16 +2493,16 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>49336</v>
+        <v>49338</v>
       </c>
       <c r="C126">
-        <v>59545</v>
+        <v>59686</v>
       </c>
       <c r="D126">
-        <v>76952</v>
+        <v>77250</v>
       </c>
       <c r="E126">
-        <v>93512</v>
+        <v>93647</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>51744</v>
+        <v>51766</v>
       </c>
       <c r="C127">
-        <v>62246</v>
+        <v>62463</v>
       </c>
       <c r="D127">
-        <v>79175</v>
+        <v>79470</v>
       </c>
       <c r="E127">
-        <v>95278</v>
+        <v>95392</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,13 +2530,13 @@
         <v>50700</v>
       </c>
       <c r="C128">
-        <v>60137</v>
+        <v>60246</v>
       </c>
       <c r="D128">
-        <v>77007</v>
+        <v>77227</v>
       </c>
       <c r="E128">
-        <v>93914</v>
+        <v>94014</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2547,13 +2547,13 @@
         <v>50700</v>
       </c>
       <c r="C129">
-        <v>60137</v>
+        <v>60246</v>
       </c>
       <c r="D129">
-        <v>77007</v>
+        <v>77227</v>
       </c>
       <c r="E129">
-        <v>93914</v>
+        <v>94014</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="C130">
-        <v>59384</v>
+        <v>59452</v>
       </c>
       <c r="D130">
-        <v>75685</v>
+        <v>75896</v>
       </c>
       <c r="E130">
-        <v>92969</v>
+        <v>93058</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="C131">
-        <v>59384</v>
+        <v>59452</v>
       </c>
       <c r="D131">
-        <v>75685</v>
+        <v>75896</v>
       </c>
       <c r="E131">
-        <v>92969</v>
+        <v>93058</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="C132">
-        <v>59384</v>
+        <v>59452</v>
       </c>
       <c r="D132">
-        <v>75685</v>
+        <v>75896</v>
       </c>
       <c r="E132">
-        <v>92969</v>
+        <v>93058</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="C133">
-        <v>59384</v>
+        <v>59452</v>
       </c>
       <c r="D133">
-        <v>75685</v>
+        <v>75896</v>
       </c>
       <c r="E133">
-        <v>92969</v>
+        <v>93058</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2629,16 +2629,16 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>51848</v>
+        <v>51855</v>
       </c>
       <c r="C134">
-        <v>60623</v>
+        <v>60737</v>
       </c>
       <c r="D134">
-        <v>76851</v>
+        <v>77110</v>
       </c>
       <c r="E134">
-        <v>93650</v>
+        <v>93743</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2646,16 +2646,16 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>50207</v>
+        <v>50209</v>
       </c>
       <c r="C135">
-        <v>58339</v>
+        <v>58420</v>
       </c>
       <c r="D135">
-        <v>74735</v>
+        <v>74965</v>
       </c>
       <c r="E135">
-        <v>92305</v>
+        <v>92404</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2663,16 +2663,16 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>49859</v>
+        <v>49861</v>
       </c>
       <c r="C136">
-        <v>57881</v>
+        <v>57991</v>
       </c>
       <c r="D136">
-        <v>74323</v>
+        <v>74565</v>
       </c>
       <c r="E136">
-        <v>91937</v>
+        <v>92047</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2680,16 +2680,16 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>49859</v>
+        <v>49861</v>
       </c>
       <c r="C137">
-        <v>57881</v>
+        <v>57991</v>
       </c>
       <c r="D137">
-        <v>74323</v>
+        <v>74565</v>
       </c>
       <c r="E137">
-        <v>91937</v>
+        <v>92047</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2697,16 +2697,16 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>49859</v>
+        <v>49861</v>
       </c>
       <c r="C138">
-        <v>57881</v>
+        <v>57991</v>
       </c>
       <c r="D138">
-        <v>74323</v>
+        <v>74565</v>
       </c>
       <c r="E138">
-        <v>91937</v>
+        <v>92047</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>49393</v>
       </c>
       <c r="C139">
-        <v>57540</v>
+        <v>57660</v>
       </c>
       <c r="D139">
-        <v>74118</v>
+        <v>74373</v>
       </c>
       <c r="E139">
-        <v>91642</v>
+        <v>91756</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2731,16 +2731,16 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>47544</v>
+        <v>47547</v>
       </c>
       <c r="C140">
-        <v>56094</v>
+        <v>56201</v>
       </c>
       <c r="D140">
-        <v>73408</v>
+        <v>73653</v>
       </c>
       <c r="E140">
-        <v>91725</v>
+        <v>91858</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2751,13 +2751,13 @@
         <v>49393</v>
       </c>
       <c r="C141">
-        <v>57540</v>
+        <v>57660</v>
       </c>
       <c r="D141">
-        <v>74118</v>
+        <v>74373</v>
       </c>
       <c r="E141">
-        <v>91642</v>
+        <v>91756</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>49393</v>
       </c>
       <c r="C142">
-        <v>57540</v>
+        <v>57660</v>
       </c>
       <c r="D142">
-        <v>74118</v>
+        <v>74373</v>
       </c>
       <c r="E142">
-        <v>91642</v>
+        <v>91756</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>49599</v>
       </c>
       <c r="C143">
-        <v>58167</v>
+        <v>58280</v>
       </c>
       <c r="D143">
-        <v>74672</v>
+        <v>74929</v>
       </c>
       <c r="E143">
-        <v>91909</v>
+        <v>92030</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>49599</v>
       </c>
       <c r="C144">
-        <v>58167</v>
+        <v>58280</v>
       </c>
       <c r="D144">
-        <v>74672</v>
+        <v>74929</v>
       </c>
       <c r="E144">
-        <v>91909</v>
+        <v>92030</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>49599</v>
       </c>
       <c r="C145">
-        <v>58167</v>
+        <v>58280</v>
       </c>
       <c r="D145">
-        <v>74672</v>
+        <v>74929</v>
       </c>
       <c r="E145">
-        <v>91909</v>
+        <v>92030</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,13 +2836,13 @@
         <v>50700</v>
       </c>
       <c r="C146">
-        <v>60137</v>
+        <v>60246</v>
       </c>
       <c r="D146">
-        <v>77007</v>
+        <v>77227</v>
       </c>
       <c r="E146">
-        <v>93914</v>
+        <v>94014</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -2853,13 +2853,13 @@
         <v>47817</v>
       </c>
       <c r="C147">
-        <v>55544</v>
+        <v>55615</v>
       </c>
       <c r="D147">
-        <v>72243</v>
+        <v>72482</v>
       </c>
       <c r="E147">
-        <v>90497</v>
+        <v>90630</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>47341</v>
       </c>
       <c r="C148">
-        <v>54676</v>
+        <v>54747</v>
       </c>
       <c r="D148">
-        <v>71087</v>
+        <v>71341</v>
       </c>
       <c r="E148">
-        <v>89406</v>
+        <v>89550</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>44683</v>
       </c>
       <c r="C149">
-        <v>51488</v>
+        <v>51522</v>
       </c>
       <c r="D149">
-        <v>67626</v>
+        <v>67899</v>
       </c>
       <c r="E149">
-        <v>86270</v>
+        <v>86463</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>44683</v>
       </c>
       <c r="C150">
-        <v>51488</v>
+        <v>51522</v>
       </c>
       <c r="D150">
-        <v>67626</v>
+        <v>67899</v>
       </c>
       <c r="E150">
-        <v>86270</v>
+        <v>86463</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>44683</v>
       </c>
       <c r="C151">
-        <v>51488</v>
+        <v>51522</v>
       </c>
       <c r="D151">
-        <v>67626</v>
+        <v>67899</v>
       </c>
       <c r="E151">
-        <v>86270</v>
+        <v>86463</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>44683</v>
       </c>
       <c r="C152">
-        <v>51488</v>
+        <v>51522</v>
       </c>
       <c r="D152">
-        <v>67626</v>
+        <v>67899</v>
       </c>
       <c r="E152">
-        <v>86270</v>
+        <v>86463</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,13 +2955,13 @@
         <v>43184</v>
       </c>
       <c r="C153">
-        <v>51375</v>
+        <v>51530</v>
       </c>
       <c r="D153">
-        <v>69170</v>
+        <v>69548</v>
       </c>
       <c r="E153">
-        <v>88547</v>
+        <v>88748</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -2972,13 +2972,13 @@
         <v>43184</v>
       </c>
       <c r="C154">
-        <v>51375</v>
+        <v>51530</v>
       </c>
       <c r="D154">
-        <v>69170</v>
+        <v>69548</v>
       </c>
       <c r="E154">
-        <v>88547</v>
+        <v>88748</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -2989,13 +2989,13 @@
         <v>41003</v>
       </c>
       <c r="C155">
-        <v>47650</v>
+        <v>47703</v>
       </c>
       <c r="D155">
-        <v>63985</v>
+        <v>64379</v>
       </c>
       <c r="E155">
-        <v>83435</v>
+        <v>83710</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>41003</v>
       </c>
       <c r="C156">
-        <v>47650</v>
+        <v>47703</v>
       </c>
       <c r="D156">
-        <v>63985</v>
+        <v>64379</v>
       </c>
       <c r="E156">
-        <v>83435</v>
+        <v>83710</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>41431</v>
       </c>
       <c r="C157">
-        <v>48427</v>
+        <v>48479</v>
       </c>
       <c r="D157">
-        <v>65099</v>
+        <v>65477</v>
       </c>
       <c r="E157">
-        <v>84639</v>
+        <v>84887</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>42497</v>
       </c>
       <c r="C158">
-        <v>49957</v>
+        <v>50057</v>
       </c>
       <c r="D158">
-        <v>66985</v>
+        <v>67356</v>
       </c>
       <c r="E158">
-        <v>86206</v>
+        <v>86451</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>42020</v>
       </c>
       <c r="C159">
-        <v>49085</v>
+        <v>49186</v>
       </c>
       <c r="D159">
-        <v>65792</v>
+        <v>66176</v>
       </c>
       <c r="E159">
-        <v>84964</v>
+        <v>85232</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>39952</v>
       </c>
       <c r="C160">
-        <v>46740</v>
+        <v>46786</v>
       </c>
       <c r="D160">
-        <v>63160</v>
+        <v>63575</v>
       </c>
       <c r="E160">
-        <v>82731</v>
+        <v>83040</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3088,16 +3088,16 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>40247</v>
+        <v>40257</v>
       </c>
       <c r="C161">
-        <v>48744</v>
+        <v>49000</v>
       </c>
       <c r="D161">
-        <v>67121</v>
+        <v>67609</v>
       </c>
       <c r="E161">
-        <v>86906</v>
+        <v>87177</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,13 +3108,13 @@
         <v>40876</v>
       </c>
       <c r="C162">
-        <v>48346</v>
+        <v>48392</v>
       </c>
       <c r="D162">
-        <v>65415</v>
+        <v>65793</v>
       </c>
       <c r="E162">
-        <v>85154</v>
+        <v>85408</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3125,13 +3125,13 @@
         <v>45523</v>
       </c>
       <c r="C163">
-        <v>52730</v>
+        <v>52804</v>
       </c>
       <c r="D163">
-        <v>68877</v>
+        <v>69182</v>
       </c>
       <c r="E163">
-        <v>87370</v>
+        <v>87568</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>45999</v>
       </c>
       <c r="C164">
-        <v>53582</v>
+        <v>53656</v>
       </c>
       <c r="D164">
-        <v>70037</v>
+        <v>70329</v>
       </c>
       <c r="E164">
-        <v>88532</v>
+        <v>88719</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>42240</v>
       </c>
       <c r="C165">
-        <v>49612</v>
+        <v>49672</v>
       </c>
       <c r="D165">
-        <v>66432</v>
+        <v>66805</v>
       </c>
       <c r="E165">
-        <v>85420</v>
+        <v>85696</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>42240</v>
       </c>
       <c r="C166">
-        <v>49612</v>
+        <v>49672</v>
       </c>
       <c r="D166">
-        <v>66432</v>
+        <v>66805</v>
       </c>
       <c r="E166">
-        <v>85420</v>
+        <v>85696</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>42008</v>
       </c>
       <c r="C167">
-        <v>50847</v>
+        <v>51118</v>
       </c>
       <c r="D167">
-        <v>69251</v>
+        <v>69774</v>
       </c>
       <c r="E167">
-        <v>88723</v>
+        <v>88981</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>42536</v>
       </c>
       <c r="C168">
-        <v>51779</v>
+        <v>52049</v>
       </c>
       <c r="D168">
-        <v>70485</v>
+        <v>70965</v>
       </c>
       <c r="E168">
-        <v>89856</v>
+        <v>90082</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3224,16 +3224,16 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>51484</v>
+        <v>51485</v>
       </c>
       <c r="C169">
-        <v>59987</v>
+        <v>60039</v>
       </c>
       <c r="D169">
-        <v>76545</v>
+        <v>76764</v>
       </c>
       <c r="E169">
-        <v>93778</v>
+        <v>93870</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>50060</v>
       </c>
       <c r="C170">
-        <v>57814</v>
+        <v>57832</v>
       </c>
       <c r="D170">
-        <v>74403</v>
+        <v>74563</v>
       </c>
       <c r="E170">
-        <v>92376</v>
+        <v>92463</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3258,16 +3258,16 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>51484</v>
+        <v>51485</v>
       </c>
       <c r="C171">
-        <v>59987</v>
+        <v>60039</v>
       </c>
       <c r="D171">
-        <v>76545</v>
+        <v>76764</v>
       </c>
       <c r="E171">
-        <v>93778</v>
+        <v>93870</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>50060</v>
       </c>
       <c r="C172">
-        <v>57814</v>
+        <v>57832</v>
       </c>
       <c r="D172">
-        <v>74403</v>
+        <v>74563</v>
       </c>
       <c r="E172">
-        <v>92376</v>
+        <v>92463</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>50060</v>
       </c>
       <c r="C173">
-        <v>57814</v>
+        <v>57832</v>
       </c>
       <c r="D173">
-        <v>74403</v>
+        <v>74563</v>
       </c>
       <c r="E173">
-        <v>92376</v>
+        <v>92463</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3309,16 +3309,16 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>49953</v>
+        <v>49955</v>
       </c>
       <c r="C174">
-        <v>57718</v>
+        <v>57751</v>
       </c>
       <c r="D174">
-        <v>73986</v>
+        <v>74160</v>
       </c>
       <c r="E174">
-        <v>91704</v>
+        <v>91792</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>50560</v>
+        <v>50562</v>
       </c>
       <c r="C175">
-        <v>59532</v>
+        <v>59595</v>
       </c>
       <c r="D175">
-        <v>76838</v>
+        <v>77033</v>
       </c>
       <c r="E175">
-        <v>94486</v>
+        <v>94572</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>50014</v>
+        <v>50017</v>
       </c>
       <c r="C176">
-        <v>58594</v>
+        <v>58659</v>
       </c>
       <c r="D176">
-        <v>75707</v>
+        <v>75916</v>
       </c>
       <c r="E176">
-        <v>93541</v>
+        <v>93636</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>50014</v>
+        <v>50017</v>
       </c>
       <c r="C177">
-        <v>58594</v>
+        <v>58659</v>
       </c>
       <c r="D177">
-        <v>75707</v>
+        <v>75916</v>
       </c>
       <c r="E177">
-        <v>93541</v>
+        <v>93636</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3377,16 +3377,16 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>49974</v>
+        <v>49975</v>
       </c>
       <c r="C178">
-        <v>57898</v>
+        <v>57944</v>
       </c>
       <c r="D178">
-        <v>74430</v>
+        <v>74609</v>
       </c>
       <c r="E178">
-        <v>92273</v>
+        <v>92367</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3397,13 +3397,13 @@
         <v>49521</v>
       </c>
       <c r="C179">
-        <v>57609</v>
+        <v>57675</v>
       </c>
       <c r="D179">
-        <v>74325</v>
+        <v>74498</v>
       </c>
       <c r="E179">
-        <v>92229</v>
+        <v>92322</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3411,16 +3411,16 @@
         <v>179</v>
       </c>
       <c r="B180">
-        <v>50572</v>
+        <v>50573</v>
       </c>
       <c r="C180">
-        <v>59463</v>
+        <v>59524</v>
       </c>
       <c r="D180">
-        <v>76596</v>
+        <v>76746</v>
       </c>
       <c r="E180">
-        <v>94193</v>
+        <v>94267</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3428,16 +3428,16 @@
         <v>180</v>
       </c>
       <c r="B181">
-        <v>50572</v>
+        <v>50573</v>
       </c>
       <c r="C181">
-        <v>59463</v>
+        <v>59524</v>
       </c>
       <c r="D181">
-        <v>76596</v>
+        <v>76746</v>
       </c>
       <c r="E181">
-        <v>94193</v>
+        <v>94267</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3445,16 +3445,16 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="C182">
-        <v>51174</v>
+        <v>51294</v>
       </c>
       <c r="D182">
-        <v>69269</v>
+        <v>69600</v>
       </c>
       <c r="E182">
-        <v>89072</v>
+        <v>89290</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3465,13 +3465,13 @@
         <v>42295</v>
       </c>
       <c r="C183">
-        <v>49418</v>
+        <v>49436</v>
       </c>
       <c r="D183">
-        <v>67219</v>
+        <v>67509</v>
       </c>
       <c r="E183">
-        <v>87372</v>
+        <v>87629</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>46575</v>
       </c>
       <c r="C184">
-        <v>55088</v>
+        <v>55110</v>
       </c>
       <c r="D184">
-        <v>72736</v>
+        <v>72970</v>
       </c>
       <c r="E184">
-        <v>91526</v>
+        <v>91687</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>46575</v>
       </c>
       <c r="C185">
-        <v>55088</v>
+        <v>55110</v>
       </c>
       <c r="D185">
-        <v>72736</v>
+        <v>72970</v>
       </c>
       <c r="E185">
-        <v>91526</v>
+        <v>91687</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,13 +3516,13 @@
         <v>42328</v>
       </c>
       <c r="C186">
-        <v>50716</v>
+        <v>50743</v>
       </c>
       <c r="D186">
-        <v>69397</v>
+        <v>69695</v>
       </c>
       <c r="E186">
-        <v>89171</v>
+        <v>89423</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3533,13 +3533,13 @@
         <v>41833</v>
       </c>
       <c r="C187">
-        <v>49749</v>
+        <v>49777</v>
       </c>
       <c r="D187">
-        <v>68170</v>
+        <v>68479</v>
       </c>
       <c r="E187">
-        <v>88019</v>
+        <v>88288</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3547,16 +3547,16 @@
         <v>187</v>
       </c>
       <c r="B188">
-        <v>42278</v>
+        <v>42279</v>
       </c>
       <c r="C188">
-        <v>50690</v>
+        <v>50867</v>
       </c>
       <c r="D188">
-        <v>69243</v>
+        <v>69722</v>
       </c>
       <c r="E188">
-        <v>89274</v>
+        <v>89509</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3564,16 +3564,16 @@
         <v>188</v>
       </c>
       <c r="B189">
-        <v>42278</v>
+        <v>42279</v>
       </c>
       <c r="C189">
-        <v>50690</v>
+        <v>50867</v>
       </c>
       <c r="D189">
-        <v>69243</v>
+        <v>69722</v>
       </c>
       <c r="E189">
-        <v>89274</v>
+        <v>89509</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3581,16 +3581,16 @@
         <v>189</v>
       </c>
       <c r="B190">
-        <v>42278</v>
+        <v>42279</v>
       </c>
       <c r="C190">
-        <v>50690</v>
+        <v>50867</v>
       </c>
       <c r="D190">
-        <v>69243</v>
+        <v>69722</v>
       </c>
       <c r="E190">
-        <v>89274</v>
+        <v>89509</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3601,13 +3601,13 @@
         <v>46385</v>
       </c>
       <c r="C191">
-        <v>55138</v>
+        <v>55189</v>
       </c>
       <c r="D191">
-        <v>73013</v>
+        <v>73301</v>
       </c>
       <c r="E191">
-        <v>91706</v>
+        <v>91894</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>41833</v>
       </c>
       <c r="C192">
-        <v>49749</v>
+        <v>49777</v>
       </c>
       <c r="D192">
-        <v>68170</v>
+        <v>68479</v>
       </c>
       <c r="E192">
-        <v>88019</v>
+        <v>88288</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>50372</v>
       </c>
       <c r="C193">
-        <v>58921</v>
+        <v>58969</v>
       </c>
       <c r="D193">
-        <v>76070</v>
+        <v>76296</v>
       </c>
       <c r="E193">
-        <v>93519</v>
+        <v>93620</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>50372</v>
       </c>
       <c r="C194">
-        <v>58921</v>
+        <v>58969</v>
       </c>
       <c r="D194">
-        <v>76070</v>
+        <v>76296</v>
       </c>
       <c r="E194">
-        <v>93519</v>
+        <v>93620</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3666,16 +3666,16 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>51484</v>
+        <v>51485</v>
       </c>
       <c r="C195">
-        <v>59987</v>
+        <v>60039</v>
       </c>
       <c r="D195">
-        <v>76545</v>
+        <v>76764</v>
       </c>
       <c r="E195">
-        <v>93778</v>
+        <v>93870</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>47422</v>
       </c>
       <c r="C196">
-        <v>55468</v>
+        <v>55493</v>
       </c>
       <c r="D196">
-        <v>72898</v>
+        <v>73115</v>
       </c>
       <c r="E196">
-        <v>91398</v>
+        <v>91515</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>47783</v>
       </c>
       <c r="C197">
-        <v>55964</v>
+        <v>56009</v>
       </c>
       <c r="D197">
-        <v>73559</v>
+        <v>73788</v>
       </c>
       <c r="E197">
-        <v>91794</v>
+        <v>91911</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>47783</v>
       </c>
       <c r="C198">
-        <v>55964</v>
+        <v>56009</v>
       </c>
       <c r="D198">
-        <v>73559</v>
+        <v>73788</v>
       </c>
       <c r="E198">
-        <v>91794</v>
+        <v>91911</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>48311</v>
       </c>
       <c r="C199">
-        <v>56966</v>
+        <v>57011</v>
       </c>
       <c r="D199">
-        <v>74796</v>
+        <v>75015</v>
       </c>
       <c r="E199">
-        <v>92841</v>
+        <v>92948</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>48311</v>
       </c>
       <c r="C200">
-        <v>56966</v>
+        <v>57011</v>
       </c>
       <c r="D200">
-        <v>74796</v>
+        <v>75015</v>
       </c>
       <c r="E200">
-        <v>92841</v>
+        <v>92948</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>48424</v>
       </c>
       <c r="C201">
-        <v>58318</v>
+        <v>58340</v>
       </c>
       <c r="D201">
-        <v>77142</v>
+        <v>77355</v>
       </c>
       <c r="E201">
-        <v>94708</v>
+        <v>94814</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,13 +3788,13 @@
         <v>46708</v>
       </c>
       <c r="C202">
-        <v>56779</v>
+        <v>56830</v>
       </c>
       <c r="D202">
-        <v>76120</v>
+        <v>76390</v>
       </c>
       <c r="E202">
-        <v>94284</v>
+        <v>94404</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3805,13 +3805,13 @@
         <v>47940</v>
       </c>
       <c r="C203">
-        <v>56428</v>
+        <v>56452</v>
       </c>
       <c r="D203">
-        <v>74063</v>
+        <v>74271</v>
       </c>
       <c r="E203">
-        <v>92424</v>
+        <v>92531</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3822,13 +3822,13 @@
         <v>45779</v>
       </c>
       <c r="C204">
-        <v>54405</v>
+        <v>54439</v>
       </c>
       <c r="D204">
-        <v>72699</v>
+        <v>72971</v>
       </c>
       <c r="E204">
-        <v>91500</v>
+        <v>91643</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3839,13 +3839,13 @@
         <v>46321</v>
       </c>
       <c r="C205">
-        <v>55398</v>
+        <v>55430</v>
       </c>
       <c r="D205">
-        <v>73891</v>
+        <v>74151</v>
       </c>
       <c r="E205">
-        <v>92524</v>
+        <v>92656</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3853,16 +3853,16 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>30313</v>
+        <v>30322</v>
       </c>
       <c r="C206">
-        <v>41091</v>
+        <v>41264</v>
       </c>
       <c r="D206">
-        <v>59163</v>
+        <v>59942</v>
       </c>
       <c r="E206">
-        <v>77259</v>
+        <v>78127</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="C207">
-        <v>38437</v>
+        <v>38534</v>
       </c>
       <c r="D207">
-        <v>55412</v>
+        <v>55993</v>
       </c>
       <c r="E207">
-        <v>73000</v>
+        <v>73815</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="C208">
-        <v>38437</v>
+        <v>38534</v>
       </c>
       <c r="D208">
-        <v>55412</v>
+        <v>55993</v>
       </c>
       <c r="E208">
-        <v>73000</v>
+        <v>73815</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3904,16 +3904,16 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>30313</v>
+        <v>30322</v>
       </c>
       <c r="C209">
-        <v>41091</v>
+        <v>41264</v>
       </c>
       <c r="D209">
-        <v>59163</v>
+        <v>59942</v>
       </c>
       <c r="E209">
-        <v>77259</v>
+        <v>78127</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="C210">
-        <v>38437</v>
+        <v>38534</v>
       </c>
       <c r="D210">
-        <v>55412</v>
+        <v>55993</v>
       </c>
       <c r="E210">
-        <v>73000</v>
+        <v>73815</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>29480</v>
       </c>
       <c r="C211">
-        <v>39305</v>
+        <v>39375</v>
       </c>
       <c r="D211">
-        <v>56737</v>
+        <v>57188</v>
       </c>
       <c r="E211">
-        <v>75027</v>
+        <v>75757</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>32117</v>
+        <v>32119</v>
       </c>
       <c r="C212">
-        <v>43170</v>
+        <v>43346</v>
       </c>
       <c r="D212">
-        <v>61540</v>
+        <v>62300</v>
       </c>
       <c r="E212">
-        <v>79852</v>
+        <v>80661</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="C213">
-        <v>38437</v>
+        <v>38534</v>
       </c>
       <c r="D213">
-        <v>55412</v>
+        <v>55993</v>
       </c>
       <c r="E213">
-        <v>73000</v>
+        <v>73815</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>27156</v>
       </c>
       <c r="C214">
-        <v>35705</v>
+        <v>35731</v>
       </c>
       <c r="D214">
-        <v>51842</v>
+        <v>52127</v>
       </c>
       <c r="E214">
-        <v>69138</v>
+        <v>69763</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>27156</v>
       </c>
       <c r="C215">
-        <v>35705</v>
+        <v>35731</v>
       </c>
       <c r="D215">
-        <v>51842</v>
+        <v>52127</v>
       </c>
       <c r="E215">
-        <v>69138</v>
+        <v>69763</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>26781</v>
       </c>
       <c r="C216">
-        <v>35005</v>
+        <v>35026</v>
       </c>
       <c r="D216">
-        <v>50715</v>
+        <v>50944</v>
       </c>
       <c r="E216">
-        <v>67733</v>
+        <v>68298</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>27300</v>
       </c>
       <c r="C217">
-        <v>36270</v>
+        <v>36313</v>
       </c>
       <c r="D217">
-        <v>53069</v>
+        <v>53409</v>
       </c>
       <c r="E217">
-        <v>70713</v>
+        <v>71376</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>27706</v>
       </c>
       <c r="C218">
-        <v>37123</v>
+        <v>37164</v>
       </c>
       <c r="D218">
-        <v>54421</v>
+        <v>54746</v>
       </c>
       <c r="E218">
-        <v>72409</v>
+        <v>73038</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>31757</v>
       </c>
       <c r="C219">
-        <v>42324</v>
+        <v>42393</v>
       </c>
       <c r="D219">
-        <v>60610</v>
+        <v>61232</v>
       </c>
       <c r="E219">
-        <v>78985</v>
+        <v>79690</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>32267</v>
+        <v>32274</v>
       </c>
       <c r="C220">
-        <v>44234</v>
+        <v>44503</v>
       </c>
       <c r="D220">
-        <v>63206</v>
+        <v>64117</v>
       </c>
       <c r="E220">
-        <v>81567</v>
+        <v>82367</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>33294</v>
       </c>
       <c r="C221">
-        <v>44394</v>
+        <v>44461</v>
       </c>
       <c r="D221">
-        <v>63239</v>
+        <v>63880</v>
       </c>
       <c r="E221">
-        <v>81692</v>
+        <v>82310</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>31757</v>
       </c>
       <c r="C222">
-        <v>42324</v>
+        <v>42393</v>
       </c>
       <c r="D222">
-        <v>60610</v>
+        <v>61232</v>
       </c>
       <c r="E222">
-        <v>78985</v>
+        <v>79690</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>33896</v>
       </c>
       <c r="C223">
-        <v>45548</v>
+        <v>45615</v>
       </c>
       <c r="D223">
-        <v>64701</v>
+        <v>65308</v>
       </c>
       <c r="E223">
-        <v>83178</v>
+        <v>83751</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4162,13 +4162,13 @@
         <v>26277</v>
       </c>
       <c r="C224">
-        <v>34823</v>
+        <v>34831</v>
       </c>
       <c r="D224">
-        <v>51294</v>
+        <v>51415</v>
       </c>
       <c r="E224">
-        <v>69216</v>
+        <v>69628</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4179,13 +4179,13 @@
         <v>25535</v>
       </c>
       <c r="C225">
-        <v>33405</v>
+        <v>33413</v>
       </c>
       <c r="D225">
-        <v>48859</v>
+        <v>48996</v>
       </c>
       <c r="E225">
-        <v>65804</v>
+        <v>66255</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4196,13 +4196,13 @@
         <v>25902</v>
       </c>
       <c r="C226">
-        <v>34104</v>
+        <v>34112</v>
       </c>
       <c r="D226">
-        <v>50073</v>
+        <v>50202</v>
       </c>
       <c r="E226">
-        <v>67519</v>
+        <v>67953</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>25880</v>
       </c>
       <c r="C227">
-        <v>33603</v>
+        <v>33620</v>
       </c>
       <c r="D227">
-        <v>48733</v>
+        <v>48905</v>
       </c>
       <c r="E227">
-        <v>65549</v>
+        <v>66045</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,13 +4230,13 @@
         <v>25055</v>
       </c>
       <c r="C228">
-        <v>33748</v>
+        <v>33756</v>
       </c>
       <c r="D228">
-        <v>51049</v>
+        <v>51150</v>
       </c>
       <c r="E228">
-        <v>70000</v>
+        <v>70360</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>32267</v>
+        <v>32274</v>
       </c>
       <c r="C229">
-        <v>44234</v>
+        <v>44503</v>
       </c>
       <c r="D229">
-        <v>63206</v>
+        <v>64117</v>
       </c>
       <c r="E229">
-        <v>81567</v>
+        <v>82367</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>32712</v>
       </c>
       <c r="C230">
-        <v>43270</v>
+        <v>43337</v>
       </c>
       <c r="D230">
-        <v>61754</v>
+        <v>62425</v>
       </c>
       <c r="E230">
-        <v>80143</v>
+        <v>80805</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>32655</v>
+        <v>32656</v>
       </c>
       <c r="C231">
-        <v>44235</v>
+        <v>44406</v>
       </c>
       <c r="D231">
-        <v>62956</v>
+        <v>63683</v>
       </c>
       <c r="E231">
-        <v>81372</v>
+        <v>82124</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>29976</v>
       </c>
       <c r="C232">
-        <v>39989</v>
+        <v>40053</v>
       </c>
       <c r="D232">
-        <v>58208</v>
+        <v>58678</v>
       </c>
       <c r="E232">
-        <v>76789</v>
+        <v>77509</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4315,13 +4315,13 @@
         <v>30438</v>
       </c>
       <c r="C233">
-        <v>40981</v>
+        <v>41044</v>
       </c>
       <c r="D233">
-        <v>59641</v>
+        <v>60087</v>
       </c>
       <c r="E233">
-        <v>78399</v>
+        <v>79073</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,13 +4332,13 @@
         <v>33727</v>
       </c>
       <c r="C234">
-        <v>44610</v>
+        <v>44678</v>
       </c>
       <c r="D234">
-        <v>62961</v>
+        <v>63493</v>
       </c>
       <c r="E234">
-        <v>81325</v>
+        <v>81939</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4349,13 +4349,13 @@
         <v>33727</v>
       </c>
       <c r="C235">
-        <v>44610</v>
+        <v>44678</v>
       </c>
       <c r="D235">
-        <v>62961</v>
+        <v>63493</v>
       </c>
       <c r="E235">
-        <v>81325</v>
+        <v>81939</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4366,13 +4366,13 @@
         <v>33727</v>
       </c>
       <c r="C236">
-        <v>44610</v>
+        <v>44678</v>
       </c>
       <c r="D236">
-        <v>62961</v>
+        <v>63493</v>
       </c>
       <c r="E236">
-        <v>81325</v>
+        <v>81939</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>26222</v>
       </c>
       <c r="C237">
-        <v>34268</v>
+        <v>34284</v>
       </c>
       <c r="D237">
-        <v>49931</v>
+        <v>50093</v>
       </c>
       <c r="E237">
-        <v>67256</v>
+        <v>67730</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>25880</v>
       </c>
       <c r="C238">
-        <v>33603</v>
+        <v>33620</v>
       </c>
       <c r="D238">
-        <v>48733</v>
+        <v>48905</v>
       </c>
       <c r="E238">
-        <v>65549</v>
+        <v>66045</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4417,13 +4417,13 @@
         <v>26570</v>
       </c>
       <c r="C239">
-        <v>34955</v>
+        <v>34969</v>
       </c>
       <c r="D239">
-        <v>51146</v>
+        <v>51299</v>
       </c>
       <c r="E239">
-        <v>68942</v>
+        <v>69391</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,13 +4434,13 @@
         <v>26363</v>
       </c>
       <c r="C240">
-        <v>34688</v>
+        <v>34705</v>
       </c>
       <c r="D240">
-        <v>50442</v>
+        <v>50608</v>
       </c>
       <c r="E240">
-        <v>67579</v>
+        <v>68010</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4451,13 +4451,13 @@
         <v>25910</v>
       </c>
       <c r="C241">
-        <v>34117</v>
+        <v>34129</v>
       </c>
       <c r="D241">
-        <v>49811</v>
+        <v>49950</v>
       </c>
       <c r="E241">
-        <v>66930</v>
+        <v>67325</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>33294</v>
       </c>
       <c r="C242">
-        <v>44394</v>
+        <v>44461</v>
       </c>
       <c r="D242">
-        <v>63239</v>
+        <v>63880</v>
       </c>
       <c r="E242">
-        <v>81692</v>
+        <v>82310</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>35406</v>
       </c>
       <c r="C243">
-        <v>46673</v>
+        <v>46816</v>
       </c>
       <c r="D243">
-        <v>65465</v>
+        <v>66234</v>
       </c>
       <c r="E243">
-        <v>83713</v>
+        <v>84261</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>33294</v>
       </c>
       <c r="C244">
-        <v>44394</v>
+        <v>44461</v>
       </c>
       <c r="D244">
-        <v>63239</v>
+        <v>63880</v>
       </c>
       <c r="E244">
-        <v>81692</v>
+        <v>82310</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,13 +4519,13 @@
         <v>36064</v>
       </c>
       <c r="C245">
-        <v>47893</v>
+        <v>48035</v>
       </c>
       <c r="D245">
-        <v>66957</v>
+        <v>67682</v>
       </c>
       <c r="E245">
-        <v>85130</v>
+        <v>85631</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4536,13 +4536,13 @@
         <v>36052</v>
       </c>
       <c r="C246">
-        <v>48846</v>
+        <v>49119</v>
       </c>
       <c r="D246">
-        <v>68446</v>
+        <v>69238</v>
       </c>
       <c r="E246">
-        <v>86632</v>
+        <v>87173</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4553,13 +4553,13 @@
         <v>36052</v>
       </c>
       <c r="C247">
-        <v>48846</v>
+        <v>49119</v>
       </c>
       <c r="D247">
-        <v>68446</v>
+        <v>69238</v>
       </c>
       <c r="E247">
-        <v>86632</v>
+        <v>87173</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4570,13 +4570,13 @@
         <v>30406</v>
       </c>
       <c r="C248">
-        <v>41104</v>
+        <v>41169</v>
       </c>
       <c r="D248">
-        <v>59432</v>
+        <v>59838</v>
       </c>
       <c r="E248">
-        <v>78210</v>
+        <v>78864</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4587,13 +4587,13 @@
         <v>25055</v>
       </c>
       <c r="C249">
-        <v>33748</v>
+        <v>33756</v>
       </c>
       <c r="D249">
-        <v>51049</v>
+        <v>51150</v>
       </c>
       <c r="E249">
-        <v>70000</v>
+        <v>70360</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>45868</v>
       </c>
       <c r="C250">
-        <v>56286</v>
+        <v>56413</v>
       </c>
       <c r="D250">
-        <v>73526</v>
+        <v>74162</v>
       </c>
       <c r="E250">
-        <v>90424</v>
+        <v>90768</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4621,13 +4621,13 @@
         <v>47677</v>
       </c>
       <c r="C251">
-        <v>58629</v>
+        <v>58895</v>
       </c>
       <c r="D251">
-        <v>75776</v>
+        <v>76312</v>
       </c>
       <c r="E251">
-        <v>92040</v>
+        <v>92340</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4638,13 +4638,13 @@
         <v>41998</v>
       </c>
       <c r="C252">
-        <v>51769</v>
+        <v>51788</v>
       </c>
       <c r="D252">
-        <v>69326</v>
+        <v>69952</v>
       </c>
       <c r="E252">
-        <v>86966</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>43819</v>
       </c>
       <c r="C253">
-        <v>54385</v>
+        <v>54484</v>
       </c>
       <c r="D253">
-        <v>72677</v>
+        <v>73135</v>
       </c>
       <c r="E253">
-        <v>90130</v>
+        <v>90452</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>47961</v>
       </c>
       <c r="C254">
-        <v>58555</v>
+        <v>58712</v>
       </c>
       <c r="D254">
-        <v>76224</v>
+        <v>76627</v>
       </c>
       <c r="E254">
-        <v>93035</v>
+        <v>93254</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>43819</v>
       </c>
       <c r="C255">
-        <v>54385</v>
+        <v>54484</v>
       </c>
       <c r="D255">
-        <v>72677</v>
+        <v>73135</v>
       </c>
       <c r="E255">
-        <v>90130</v>
+        <v>90452</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4706,13 +4706,13 @@
         <v>39352</v>
       </c>
       <c r="C256">
-        <v>49524</v>
+        <v>49530</v>
       </c>
       <c r="D256">
-        <v>67456</v>
+        <v>68063</v>
       </c>
       <c r="E256">
-        <v>85509</v>
+        <v>85963</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4726,10 +4726,10 @@
         <v>43116</v>
       </c>
       <c r="D257">
-        <v>61492</v>
+        <v>61951</v>
       </c>
       <c r="E257">
-        <v>80467</v>
+        <v>80953</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>45818</v>
       </c>
       <c r="D258">
-        <v>62882</v>
+        <v>63007</v>
       </c>
       <c r="E258">
-        <v>81284</v>
+        <v>81546</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>45818</v>
       </c>
       <c r="D259">
-        <v>62882</v>
+        <v>63007</v>
       </c>
       <c r="E259">
-        <v>81284</v>
+        <v>81546</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4774,13 +4774,13 @@
         <v>14464</v>
       </c>
       <c r="C260">
-        <v>22135</v>
+        <v>22143</v>
       </c>
       <c r="D260">
-        <v>45219</v>
+        <v>45607</v>
       </c>
       <c r="E260">
-        <v>70609</v>
+        <v>71266</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>13332</v>
       </c>
       <c r="D261">
-        <v>34027</v>
+        <v>34098</v>
       </c>
       <c r="E261">
-        <v>58784</v>
+        <v>59083</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4808,13 +4808,13 @@
         <v>13548</v>
       </c>
       <c r="C262">
-        <v>20072</v>
+        <v>20075</v>
       </c>
       <c r="D262">
-        <v>41906</v>
+        <v>42200</v>
       </c>
       <c r="E262">
-        <v>66988</v>
+        <v>67575</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,13 +4825,13 @@
         <v>13830</v>
       </c>
       <c r="C263">
-        <v>20801</v>
+        <v>20804</v>
       </c>
       <c r="D263">
-        <v>43261</v>
+        <v>43542</v>
       </c>
       <c r="E263">
-        <v>68685</v>
+        <v>69242</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4842,13 +4842,13 @@
         <v>12118</v>
       </c>
       <c r="C264">
-        <v>17938</v>
+        <v>17939</v>
       </c>
       <c r="D264">
-        <v>39307</v>
+        <v>39482</v>
       </c>
       <c r="E264">
-        <v>64299</v>
+        <v>64769</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4859,13 +4859,13 @@
         <v>12118</v>
       </c>
       <c r="C265">
-        <v>17938</v>
+        <v>17939</v>
       </c>
       <c r="D265">
-        <v>39307</v>
+        <v>39482</v>
       </c>
       <c r="E265">
-        <v>64299</v>
+        <v>64769</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>17662</v>
       </c>
       <c r="C266">
-        <v>26582</v>
+        <v>26630</v>
       </c>
       <c r="D266">
-        <v>50172</v>
+        <v>50727</v>
       </c>
       <c r="E266">
-        <v>75536</v>
+        <v>76185</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4893,13 +4893,13 @@
         <v>12118</v>
       </c>
       <c r="C267">
-        <v>17938</v>
+        <v>17939</v>
       </c>
       <c r="D267">
-        <v>39307</v>
+        <v>39482</v>
       </c>
       <c r="E267">
-        <v>64299</v>
+        <v>64769</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>13332</v>
       </c>
       <c r="D268">
-        <v>34027</v>
+        <v>34098</v>
       </c>
       <c r="E268">
-        <v>58784</v>
+        <v>59083</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>13332</v>
       </c>
       <c r="D269">
-        <v>34027</v>
+        <v>34098</v>
       </c>
       <c r="E269">
-        <v>58784</v>
+        <v>59083</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4944,13 +4944,13 @@
         <v>9610</v>
       </c>
       <c r="C270">
-        <v>16856</v>
+        <v>16864</v>
       </c>
       <c r="D270">
-        <v>39258</v>
+        <v>39402</v>
       </c>
       <c r="E270">
-        <v>63799</v>
+        <v>64236</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4961,13 +4961,13 @@
         <v>7380</v>
       </c>
       <c r="C271">
-        <v>12793</v>
+        <v>12795</v>
       </c>
       <c r="D271">
-        <v>32035</v>
+        <v>32078</v>
       </c>
       <c r="E271">
-        <v>54334</v>
+        <v>54529</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4978,13 +4978,13 @@
         <v>7380</v>
       </c>
       <c r="C272">
-        <v>12793</v>
+        <v>12795</v>
       </c>
       <c r="D272">
-        <v>32035</v>
+        <v>32078</v>
       </c>
       <c r="E272">
-        <v>54334</v>
+        <v>54529</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>10571</v>
       </c>
       <c r="C273">
-        <v>18449</v>
+        <v>18467</v>
       </c>
       <c r="D273">
-        <v>41823</v>
+        <v>42053</v>
       </c>
       <c r="E273">
-        <v>67002</v>
+        <v>67537</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>10571</v>
       </c>
       <c r="C274">
-        <v>18449</v>
+        <v>18467</v>
       </c>
       <c r="D274">
-        <v>41823</v>
+        <v>42053</v>
       </c>
       <c r="E274">
-        <v>67002</v>
+        <v>67537</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5032,10 +5032,10 @@
         <v>18344</v>
       </c>
       <c r="D275">
-        <v>36894</v>
+        <v>36953</v>
       </c>
       <c r="E275">
-        <v>56047</v>
+        <v>56180</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>13925</v>
       </c>
       <c r="D276">
-        <v>31804</v>
+        <v>31823</v>
       </c>
       <c r="E276">
-        <v>49751</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5066,10 +5066,10 @@
         <v>24013</v>
       </c>
       <c r="D277">
-        <v>44178</v>
+        <v>44291</v>
       </c>
       <c r="E277">
-        <v>65129</v>
+        <v>65356</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>23275</v>
       </c>
       <c r="C278">
-        <v>32873</v>
+        <v>32882</v>
       </c>
       <c r="D278">
-        <v>53645</v>
+        <v>53849</v>
       </c>
       <c r="E278">
-        <v>75455</v>
+        <v>75901</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>34619</v>
       </c>
       <c r="D279">
-        <v>52617</v>
+        <v>52715</v>
       </c>
       <c r="E279">
-        <v>72145</v>
+        <v>72427</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>34619</v>
       </c>
       <c r="D280">
-        <v>52617</v>
+        <v>52715</v>
       </c>
       <c r="E280">
-        <v>72145</v>
+        <v>72427</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5134,10 +5134,10 @@
         <v>15283</v>
       </c>
       <c r="D281">
-        <v>34308</v>
+        <v>34344</v>
       </c>
       <c r="E281">
-        <v>53344</v>
+        <v>53435</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5148,13 +5148,13 @@
         <v>7722</v>
       </c>
       <c r="C282">
-        <v>13260</v>
+        <v>13265</v>
       </c>
       <c r="D282">
-        <v>31332</v>
+        <v>31355</v>
       </c>
       <c r="E282">
-        <v>49210</v>
+        <v>49271</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5165,13 +5165,13 @@
         <v>7722</v>
       </c>
       <c r="C283">
-        <v>13260</v>
+        <v>13265</v>
       </c>
       <c r="D283">
-        <v>31332</v>
+        <v>31355</v>
       </c>
       <c r="E283">
-        <v>49210</v>
+        <v>49271</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5182,13 +5182,13 @@
         <v>7722</v>
       </c>
       <c r="C284">
-        <v>13260</v>
+        <v>13265</v>
       </c>
       <c r="D284">
-        <v>31332</v>
+        <v>31355</v>
       </c>
       <c r="E284">
-        <v>49210</v>
+        <v>49271</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>13925</v>
       </c>
       <c r="D285">
-        <v>31804</v>
+        <v>31823</v>
       </c>
       <c r="E285">
-        <v>49751</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>34619</v>
       </c>
       <c r="D286">
-        <v>52617</v>
+        <v>52715</v>
       </c>
       <c r="E286">
-        <v>72145</v>
+        <v>72427</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5233,13 +5233,13 @@
         <v>33355</v>
       </c>
       <c r="C287">
-        <v>42225</v>
+        <v>42471</v>
       </c>
       <c r="D287">
-        <v>62333</v>
+        <v>63021</v>
       </c>
       <c r="E287">
-        <v>84191</v>
+        <v>84567</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5250,13 +5250,13 @@
         <v>26614</v>
       </c>
       <c r="C288">
-        <v>36079</v>
+        <v>36343</v>
       </c>
       <c r="D288">
-        <v>57480</v>
+        <v>58224</v>
       </c>
       <c r="E288">
-        <v>80091</v>
+        <v>80646</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5267,13 +5267,13 @@
         <v>36602</v>
       </c>
       <c r="C289">
-        <v>45052</v>
+        <v>45201</v>
       </c>
       <c r="D289">
-        <v>64439</v>
+        <v>64971</v>
       </c>
       <c r="E289">
-        <v>85644</v>
+        <v>86004</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5284,13 +5284,13 @@
         <v>33355</v>
       </c>
       <c r="C290">
-        <v>42225</v>
+        <v>42471</v>
       </c>
       <c r="D290">
-        <v>62333</v>
+        <v>63021</v>
       </c>
       <c r="E290">
-        <v>84191</v>
+        <v>84567</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,13 +5301,13 @@
         <v>23966</v>
       </c>
       <c r="C291">
-        <v>32942</v>
+        <v>33126</v>
       </c>
       <c r="D291">
-        <v>54372</v>
+        <v>55065</v>
       </c>
       <c r="E291">
-        <v>77100</v>
+        <v>77698</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5318,13 +5318,13 @@
         <v>28495</v>
       </c>
       <c r="C292">
-        <v>37291</v>
+        <v>37342</v>
       </c>
       <c r="D292">
-        <v>56893</v>
+        <v>57504</v>
       </c>
       <c r="E292">
-        <v>77722</v>
+        <v>78256</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5335,13 +5335,13 @@
         <v>28821</v>
       </c>
       <c r="C293">
-        <v>37884</v>
+        <v>37919</v>
       </c>
       <c r="D293">
-        <v>57873</v>
+        <v>58490</v>
       </c>
       <c r="E293">
-        <v>78995</v>
+        <v>79532</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5352,13 +5352,13 @@
         <v>28495</v>
       </c>
       <c r="C294">
-        <v>37291</v>
+        <v>37342</v>
       </c>
       <c r="D294">
-        <v>56893</v>
+        <v>57504</v>
       </c>
       <c r="E294">
-        <v>77722</v>
+        <v>78256</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>24241</v>
       </c>
       <c r="C295">
-        <v>31069</v>
+        <v>31079</v>
       </c>
       <c r="D295">
-        <v>51252</v>
+        <v>51717</v>
       </c>
       <c r="E295">
-        <v>73699</v>
+        <v>74241</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>25994</v>
       </c>
       <c r="C296">
-        <v>33635</v>
+        <v>33739</v>
       </c>
       <c r="D296">
-        <v>54754</v>
+        <v>55375</v>
       </c>
       <c r="E296">
-        <v>77478</v>
+        <v>78014</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>25760</v>
       </c>
       <c r="C297">
-        <v>34766</v>
+        <v>34925</v>
       </c>
       <c r="D297">
-        <v>57389</v>
+        <v>58043</v>
       </c>
       <c r="E297">
-        <v>80369</v>
+        <v>80885</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>22445</v>
       </c>
       <c r="C298">
-        <v>30141</v>
+        <v>30244</v>
       </c>
       <c r="D298">
-        <v>51236</v>
+        <v>51844</v>
       </c>
       <c r="E298">
-        <v>74047</v>
+        <v>74644</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>22496</v>
       </c>
       <c r="C299">
-        <v>30866</v>
+        <v>30974</v>
       </c>
       <c r="D299">
-        <v>53045</v>
+        <v>53608</v>
       </c>
       <c r="E299">
-        <v>76241</v>
+        <v>76816</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>24241</v>
       </c>
       <c r="C300">
-        <v>31069</v>
+        <v>31079</v>
       </c>
       <c r="D300">
-        <v>51252</v>
+        <v>51717</v>
       </c>
       <c r="E300">
-        <v>73699</v>
+        <v>74241</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>26446</v>
       </c>
       <c r="C301">
-        <v>34601</v>
+        <v>34705</v>
       </c>
       <c r="D301">
-        <v>56268</v>
+        <v>56861</v>
       </c>
       <c r="E301">
-        <v>79112</v>
+        <v>79607</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,13 +5488,13 @@
         <v>23340</v>
       </c>
       <c r="C302">
-        <v>32052</v>
+        <v>32153</v>
       </c>
       <c r="D302">
-        <v>54201</v>
+        <v>54749</v>
       </c>
       <c r="E302">
-        <v>77426</v>
+        <v>77938</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5505,13 +5505,13 @@
         <v>23340</v>
       </c>
       <c r="C303">
-        <v>32052</v>
+        <v>32153</v>
       </c>
       <c r="D303">
-        <v>54201</v>
+        <v>54749</v>
       </c>
       <c r="E303">
-        <v>77426</v>
+        <v>77938</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>22029</v>
       </c>
       <c r="C304">
-        <v>29065</v>
+        <v>29102</v>
       </c>
       <c r="D304">
-        <v>49740</v>
+        <v>50153</v>
       </c>
       <c r="E304">
-        <v>72448</v>
+        <v>72994</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>22029</v>
       </c>
       <c r="C305">
-        <v>29065</v>
+        <v>29102</v>
       </c>
       <c r="D305">
-        <v>49740</v>
+        <v>50153</v>
       </c>
       <c r="E305">
-        <v>72448</v>
+        <v>72994</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>24090</v>
       </c>
       <c r="C306">
-        <v>29240</v>
+        <v>29243</v>
       </c>
       <c r="D306">
-        <v>47452</v>
+        <v>47615</v>
       </c>
       <c r="E306">
-        <v>69015</v>
+        <v>69438</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>22029</v>
       </c>
       <c r="C307">
-        <v>29065</v>
+        <v>29102</v>
       </c>
       <c r="D307">
-        <v>49740</v>
+        <v>50153</v>
       </c>
       <c r="E307">
-        <v>72448</v>
+        <v>72994</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5590,13 +5590,13 @@
         <v>24366</v>
       </c>
       <c r="C308">
-        <v>29922</v>
+        <v>29924</v>
       </c>
       <c r="D308">
-        <v>48781</v>
+        <v>48940</v>
       </c>
       <c r="E308">
-        <v>70755</v>
+        <v>71153</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5607,13 +5607,13 @@
         <v>24090</v>
       </c>
       <c r="C309">
-        <v>29240</v>
+        <v>29243</v>
       </c>
       <c r="D309">
-        <v>47452</v>
+        <v>47615</v>
       </c>
       <c r="E309">
-        <v>69015</v>
+        <v>69438</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,13 +5624,13 @@
         <v>22410</v>
       </c>
       <c r="C310">
-        <v>29943</v>
+        <v>29979</v>
       </c>
       <c r="D310">
-        <v>51210</v>
+        <v>51603</v>
       </c>
       <c r="E310">
-        <v>74202</v>
+        <v>74712</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5644,10 +5644,10 @@
         <v>15362</v>
       </c>
       <c r="D311">
-        <v>33203</v>
+        <v>33258</v>
       </c>
       <c r="E311">
-        <v>54264</v>
+        <v>54527</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5661,10 +5661,10 @@
         <v>15362</v>
       </c>
       <c r="D312">
-        <v>33203</v>
+        <v>33258</v>
       </c>
       <c r="E312">
-        <v>54264</v>
+        <v>54527</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5678,10 +5678,10 @@
         <v>15362</v>
       </c>
       <c r="D313">
-        <v>33203</v>
+        <v>33258</v>
       </c>
       <c r="E313">
-        <v>54264</v>
+        <v>54527</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5695,10 +5695,10 @@
         <v>15362</v>
       </c>
       <c r="D314">
-        <v>33203</v>
+        <v>33258</v>
       </c>
       <c r="E314">
-        <v>54264</v>
+        <v>54527</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>37194</v>
       </c>
       <c r="C315">
-        <v>46084</v>
+        <v>46214</v>
       </c>
       <c r="D315">
-        <v>65708</v>
+        <v>66344</v>
       </c>
       <c r="E315">
-        <v>86350</v>
+        <v>86711</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5726,13 +5726,13 @@
         <v>43477</v>
       </c>
       <c r="C316">
-        <v>52210</v>
+        <v>52305</v>
       </c>
       <c r="D316">
-        <v>70681</v>
+        <v>71107</v>
       </c>
       <c r="E316">
-        <v>89950</v>
+        <v>90184</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>43696</v>
       </c>
       <c r="C317">
-        <v>51735</v>
+        <v>51796</v>
       </c>
       <c r="D317">
-        <v>69664</v>
+        <v>69985</v>
       </c>
       <c r="E317">
-        <v>88956</v>
+        <v>89161</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>40642</v>
       </c>
       <c r="C318">
-        <v>49083</v>
+        <v>49226</v>
       </c>
       <c r="D318">
-        <v>68062</v>
+        <v>68574</v>
       </c>
       <c r="E318">
-        <v>88175</v>
+        <v>88470</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>36144</v>
       </c>
       <c r="C319">
-        <v>44182</v>
+        <v>44269</v>
       </c>
       <c r="D319">
-        <v>63134</v>
+        <v>63727</v>
       </c>
       <c r="E319">
-        <v>83758</v>
+        <v>84186</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>37254</v>
       </c>
       <c r="C320">
-        <v>45822</v>
+        <v>46006</v>
       </c>
       <c r="D320">
-        <v>65112</v>
+        <v>65771</v>
       </c>
       <c r="E320">
-        <v>85774</v>
+        <v>86151</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>40514</v>
       </c>
       <c r="C321">
-        <v>48858</v>
+        <v>48982</v>
       </c>
       <c r="D321">
-        <v>67518</v>
+        <v>68009</v>
       </c>
       <c r="E321">
-        <v>87525</v>
+        <v>87828</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>35043</v>
       </c>
       <c r="C322">
-        <v>44221</v>
+        <v>44339</v>
       </c>
       <c r="D322">
-        <v>64499</v>
+        <v>65166</v>
       </c>
       <c r="E322">
-        <v>85645</v>
+        <v>86015</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>37015</v>
       </c>
       <c r="C323">
-        <v>45134</v>
+        <v>45233</v>
       </c>
       <c r="D323">
-        <v>64225</v>
+        <v>64803</v>
       </c>
       <c r="E323">
-        <v>84965</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>37015</v>
       </c>
       <c r="C324">
-        <v>45134</v>
+        <v>45233</v>
       </c>
       <c r="D324">
-        <v>64225</v>
+        <v>64803</v>
       </c>
       <c r="E324">
-        <v>84965</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>37015</v>
       </c>
       <c r="C325">
-        <v>45134</v>
+        <v>45233</v>
       </c>
       <c r="D325">
-        <v>64225</v>
+        <v>64803</v>
       </c>
       <c r="E325">
-        <v>84965</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>42518</v>
       </c>
       <c r="C326">
-        <v>50985</v>
+        <v>51093</v>
       </c>
       <c r="D326">
-        <v>69146</v>
+        <v>69578</v>
       </c>
       <c r="E326">
-        <v>88565</v>
+        <v>88829</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,13 +5913,13 @@
         <v>33429</v>
       </c>
       <c r="C327">
-        <v>42615</v>
+        <v>42646</v>
       </c>
       <c r="D327">
-        <v>62598</v>
+        <v>63207</v>
       </c>
       <c r="E327">
-        <v>83623</v>
+        <v>84038</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -5930,13 +5930,13 @@
         <v>33429</v>
       </c>
       <c r="C328">
-        <v>42615</v>
+        <v>42646</v>
       </c>
       <c r="D328">
-        <v>62598</v>
+        <v>63207</v>
       </c>
       <c r="E328">
-        <v>83623</v>
+        <v>84038</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>30858</v>
       </c>
       <c r="C329">
-        <v>39761</v>
+        <v>39779</v>
       </c>
       <c r="D329">
-        <v>60227</v>
+        <v>60776</v>
       </c>
       <c r="E329">
-        <v>81852</v>
+        <v>82299</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>33429</v>
       </c>
       <c r="C330">
-        <v>42615</v>
+        <v>42646</v>
       </c>
       <c r="D330">
-        <v>62598</v>
+        <v>63207</v>
       </c>
       <c r="E330">
-        <v>83623</v>
+        <v>84038</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>32882</v>
       </c>
       <c r="C331">
-        <v>41581</v>
+        <v>41613</v>
       </c>
       <c r="D331">
-        <v>61271</v>
+        <v>61900</v>
       </c>
       <c r="E331">
-        <v>82267</v>
+        <v>82723</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,13 +5998,13 @@
         <v>38087</v>
       </c>
       <c r="C332">
-        <v>46930</v>
+        <v>46944</v>
       </c>
       <c r="D332">
-        <v>67296</v>
+        <v>67688</v>
       </c>
       <c r="E332">
-        <v>87939</v>
+        <v>88254</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6015,13 +6015,13 @@
         <v>39731</v>
       </c>
       <c r="C333">
-        <v>49026</v>
+        <v>49073</v>
       </c>
       <c r="D333">
-        <v>69881</v>
+        <v>70280</v>
       </c>
       <c r="E333">
-        <v>89982</v>
+        <v>90258</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,13 +6032,13 @@
         <v>43384</v>
       </c>
       <c r="C334">
-        <v>53721</v>
+        <v>53748</v>
       </c>
       <c r="D334">
-        <v>74341</v>
+        <v>74664</v>
       </c>
       <c r="E334">
-        <v>93206</v>
+        <v>93406</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6049,13 +6049,13 @@
         <v>40088</v>
       </c>
       <c r="C335">
-        <v>50519</v>
+        <v>50568</v>
       </c>
       <c r="D335">
-        <v>71924</v>
+        <v>72365</v>
       </c>
       <c r="E335">
-        <v>91627</v>
+        <v>91867</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6066,13 +6066,13 @@
         <v>35767</v>
       </c>
       <c r="C336">
-        <v>44061</v>
+        <v>44067</v>
       </c>
       <c r="D336">
-        <v>64196</v>
+        <v>64581</v>
       </c>
       <c r="E336">
-        <v>85185</v>
+        <v>85555</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6083,13 +6083,13 @@
         <v>15615</v>
       </c>
       <c r="C337">
-        <v>21904</v>
+        <v>21906</v>
       </c>
       <c r="D337">
-        <v>35223</v>
+        <v>35345</v>
       </c>
       <c r="E337">
-        <v>48399</v>
+        <v>48497</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6100,13 +6100,13 @@
         <v>13787</v>
       </c>
       <c r="C338">
-        <v>19976</v>
+        <v>19978</v>
       </c>
       <c r="D338">
-        <v>33779</v>
+        <v>33894</v>
       </c>
       <c r="E338">
-        <v>47207</v>
+        <v>47292</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6117,13 +6117,13 @@
         <v>15615</v>
       </c>
       <c r="C339">
-        <v>21904</v>
+        <v>21906</v>
       </c>
       <c r="D339">
-        <v>35223</v>
+        <v>35345</v>
       </c>
       <c r="E339">
-        <v>48399</v>
+        <v>48497</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>18776</v>
       </c>
       <c r="D340">
-        <v>32397</v>
+        <v>32482</v>
       </c>
       <c r="E340">
-        <v>45294</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,10 +6154,10 @@
         <v>18776</v>
       </c>
       <c r="D341">
-        <v>32397</v>
+        <v>32482</v>
       </c>
       <c r="E341">
-        <v>45294</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6168,13 +6168,13 @@
         <v>14382</v>
       </c>
       <c r="C342">
-        <v>21236</v>
+        <v>21305</v>
       </c>
       <c r="D342">
-        <v>36003</v>
+        <v>36118</v>
       </c>
       <c r="E342">
-        <v>50482</v>
+        <v>50580</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>14382</v>
       </c>
       <c r="C343">
-        <v>21236</v>
+        <v>21305</v>
       </c>
       <c r="D343">
-        <v>36003</v>
+        <v>36118</v>
       </c>
       <c r="E343">
-        <v>50482</v>
+        <v>50580</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>18776</v>
       </c>
       <c r="D344">
-        <v>32397</v>
+        <v>32482</v>
       </c>
       <c r="E344">
-        <v>45294</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>14331</v>
       </c>
       <c r="D345">
-        <v>27951</v>
+        <v>27997</v>
       </c>
       <c r="E345">
-        <v>40260</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>14331</v>
       </c>
       <c r="D346">
-        <v>27951</v>
+        <v>27997</v>
       </c>
       <c r="E346">
-        <v>40260</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>14331</v>
       </c>
       <c r="D347">
-        <v>27951</v>
+        <v>27997</v>
       </c>
       <c r="E347">
-        <v>40260</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6273,10 +6273,10 @@
         <v>23268</v>
       </c>
       <c r="D348">
-        <v>35997</v>
+        <v>36036</v>
       </c>
       <c r="E348">
-        <v>48462</v>
+        <v>48530</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6290,10 +6290,10 @@
         <v>23268</v>
       </c>
       <c r="D349">
-        <v>35997</v>
+        <v>36036</v>
       </c>
       <c r="E349">
-        <v>48462</v>
+        <v>48530</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6307,10 +6307,10 @@
         <v>23268</v>
       </c>
       <c r="D350">
-        <v>35997</v>
+        <v>36036</v>
       </c>
       <c r="E350">
-        <v>48462</v>
+        <v>48530</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6321,13 +6321,13 @@
         <v>7351</v>
       </c>
       <c r="C351">
-        <v>12853</v>
+        <v>12857</v>
       </c>
       <c r="D351">
-        <v>26498</v>
+        <v>26525</v>
       </c>
       <c r="E351">
-        <v>37665</v>
+        <v>37696</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6338,13 +6338,13 @@
         <v>7351</v>
       </c>
       <c r="C352">
-        <v>12853</v>
+        <v>12857</v>
       </c>
       <c r="D352">
-        <v>26498</v>
+        <v>26525</v>
       </c>
       <c r="E352">
-        <v>37665</v>
+        <v>37696</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6355,13 +6355,13 @@
         <v>23241</v>
       </c>
       <c r="C353">
-        <v>30224</v>
+        <v>30231</v>
       </c>
       <c r="D353">
-        <v>44141</v>
+        <v>44210</v>
       </c>
       <c r="E353">
-        <v>59807</v>
+        <v>59994</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6375,10 +6375,10 @@
         <v>26957</v>
       </c>
       <c r="D354">
-        <v>38645</v>
+        <v>38659</v>
       </c>
       <c r="E354">
-        <v>51570</v>
+        <v>51646</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6389,13 +6389,13 @@
         <v>23241</v>
       </c>
       <c r="C355">
-        <v>30224</v>
+        <v>30231</v>
       </c>
       <c r="D355">
-        <v>44141</v>
+        <v>44210</v>
       </c>
       <c r="E355">
-        <v>59807</v>
+        <v>59994</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6409,10 +6409,10 @@
         <v>22887</v>
       </c>
       <c r="D356">
-        <v>35684</v>
+        <v>35746</v>
       </c>
       <c r="E356">
-        <v>48147</v>
+        <v>48200</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6426,10 +6426,10 @@
         <v>22887</v>
       </c>
       <c r="D357">
-        <v>35684</v>
+        <v>35746</v>
       </c>
       <c r="E357">
-        <v>48147</v>
+        <v>48200</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6443,10 +6443,10 @@
         <v>22887</v>
       </c>
       <c r="D358">
-        <v>35684</v>
+        <v>35746</v>
       </c>
       <c r="E358">
-        <v>48147</v>
+        <v>48200</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6457,13 +6457,13 @@
         <v>8036</v>
       </c>
       <c r="C359">
-        <v>13554</v>
+        <v>13559</v>
       </c>
       <c r="D359">
-        <v>27385</v>
+        <v>27409</v>
       </c>
       <c r="E359">
-        <v>38921</v>
+        <v>38946</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6474,13 +6474,13 @@
         <v>8036</v>
       </c>
       <c r="C360">
-        <v>13554</v>
+        <v>13559</v>
       </c>
       <c r="D360">
-        <v>27385</v>
+        <v>27409</v>
       </c>
       <c r="E360">
-        <v>38921</v>
+        <v>38946</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6491,13 +6491,13 @@
         <v>22484</v>
       </c>
       <c r="C361">
-        <v>31710</v>
+        <v>31711</v>
       </c>
       <c r="D361">
-        <v>56062</v>
+        <v>56397</v>
       </c>
       <c r="E361">
-        <v>79784</v>
+        <v>80268</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6508,13 +6508,13 @@
         <v>18817</v>
       </c>
       <c r="C362">
-        <v>28369</v>
+        <v>28376</v>
       </c>
       <c r="D362">
-        <v>53355</v>
+        <v>53765</v>
       </c>
       <c r="E362">
-        <v>77791</v>
+        <v>78339</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>27058</v>
       </c>
       <c r="D363">
-        <v>49906</v>
+        <v>50013</v>
       </c>
       <c r="E363">
-        <v>74271</v>
+        <v>74678</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6542,13 +6542,13 @@
         <v>17789</v>
       </c>
       <c r="C364">
-        <v>26906</v>
+        <v>26999</v>
       </c>
       <c r="D364">
-        <v>51898</v>
+        <v>52431</v>
       </c>
       <c r="E364">
-        <v>77398</v>
+        <v>78040</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6559,13 +6559,13 @@
         <v>17789</v>
       </c>
       <c r="C365">
-        <v>26906</v>
+        <v>26999</v>
       </c>
       <c r="D365">
-        <v>51898</v>
+        <v>52431</v>
       </c>
       <c r="E365">
-        <v>77398</v>
+        <v>78040</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>12743</v>
       </c>
       <c r="C366">
-        <v>21023</v>
+        <v>21098</v>
       </c>
       <c r="D366">
-        <v>45457</v>
+        <v>45888</v>
       </c>
       <c r="E366">
-        <v>71416</v>
+        <v>72062</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6593,13 +6593,13 @@
         <v>12743</v>
       </c>
       <c r="C367">
-        <v>21023</v>
+        <v>21098</v>
       </c>
       <c r="D367">
-        <v>45457</v>
+        <v>45888</v>
       </c>
       <c r="E367">
-        <v>71416</v>
+        <v>72062</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6610,13 +6610,13 @@
         <v>13922</v>
       </c>
       <c r="C368">
-        <v>21842</v>
+        <v>21920</v>
       </c>
       <c r="D368">
-        <v>46135</v>
+        <v>46562</v>
       </c>
       <c r="E368">
-        <v>72032</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6627,13 +6627,13 @@
         <v>12743</v>
       </c>
       <c r="C369">
-        <v>21023</v>
+        <v>21098</v>
       </c>
       <c r="D369">
-        <v>45457</v>
+        <v>45888</v>
       </c>
       <c r="E369">
-        <v>71416</v>
+        <v>72062</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>11703</v>
       </c>
       <c r="C370">
-        <v>18685</v>
+        <v>18691</v>
       </c>
       <c r="D370">
-        <v>41617</v>
+        <v>41793</v>
       </c>
       <c r="E370">
-        <v>66588</v>
+        <v>67073</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>11703</v>
       </c>
       <c r="C371">
-        <v>18685</v>
+        <v>18691</v>
       </c>
       <c r="D371">
-        <v>41617</v>
+        <v>41793</v>
       </c>
       <c r="E371">
-        <v>66588</v>
+        <v>67073</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>11703</v>
       </c>
       <c r="C372">
-        <v>18685</v>
+        <v>18691</v>
       </c>
       <c r="D372">
-        <v>41617</v>
+        <v>41793</v>
       </c>
       <c r="E372">
-        <v>66588</v>
+        <v>67073</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6698,10 +6698,10 @@
         <v>31485</v>
       </c>
       <c r="D373">
-        <v>47975</v>
+        <v>48103</v>
       </c>
       <c r="E373">
-        <v>65544</v>
+        <v>65875</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6715,10 +6715,10 @@
         <v>26800</v>
       </c>
       <c r="D374">
-        <v>42114</v>
+        <v>42210</v>
       </c>
       <c r="E374">
-        <v>58856</v>
+        <v>59019</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6732,10 +6732,10 @@
         <v>31485</v>
       </c>
       <c r="D375">
-        <v>47975</v>
+        <v>48103</v>
       </c>
       <c r="E375">
-        <v>65544</v>
+        <v>65875</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>20038</v>
       </c>
       <c r="C376">
-        <v>26844</v>
+        <v>26847</v>
       </c>
       <c r="D376">
-        <v>42605</v>
+        <v>42717</v>
       </c>
       <c r="E376">
-        <v>59796</v>
+        <v>60007</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>20038</v>
       </c>
       <c r="C377">
-        <v>26844</v>
+        <v>26847</v>
       </c>
       <c r="D377">
-        <v>42605</v>
+        <v>42717</v>
       </c>
       <c r="E377">
-        <v>59796</v>
+        <v>60007</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6780,13 +6780,13 @@
         <v>27899</v>
       </c>
       <c r="C378">
-        <v>36413</v>
+        <v>36415</v>
       </c>
       <c r="D378">
-        <v>53406</v>
+        <v>53582</v>
       </c>
       <c r="E378">
-        <v>71509</v>
+        <v>71978</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6797,13 +6797,13 @@
         <v>27899</v>
       </c>
       <c r="C379">
-        <v>36413</v>
+        <v>36415</v>
       </c>
       <c r="D379">
-        <v>53406</v>
+        <v>53582</v>
       </c>
       <c r="E379">
-        <v>71509</v>
+        <v>71978</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6814,13 +6814,13 @@
         <v>27899</v>
       </c>
       <c r="C380">
-        <v>36413</v>
+        <v>36415</v>
       </c>
       <c r="D380">
-        <v>53406</v>
+        <v>53582</v>
       </c>
       <c r="E380">
-        <v>71509</v>
+        <v>71978</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6831,13 +6831,13 @@
         <v>27899</v>
       </c>
       <c r="C381">
-        <v>36413</v>
+        <v>36415</v>
       </c>
       <c r="D381">
-        <v>53406</v>
+        <v>53582</v>
       </c>
       <c r="E381">
-        <v>71509</v>
+        <v>71978</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>25104</v>
       </c>
       <c r="C382">
-        <v>33060</v>
+        <v>33067</v>
       </c>
       <c r="D382">
-        <v>49431</v>
+        <v>49555</v>
       </c>
       <c r="E382">
-        <v>67288</v>
+        <v>67688</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6868,10 +6868,10 @@
         <v>35087</v>
       </c>
       <c r="D383">
-        <v>53210</v>
+        <v>53459</v>
       </c>
       <c r="E383">
-        <v>72313</v>
+        <v>72763</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6885,10 +6885,10 @@
         <v>31606</v>
       </c>
       <c r="D384">
-        <v>49326</v>
+        <v>49495</v>
       </c>
       <c r="E384">
-        <v>68261</v>
+        <v>68648</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6899,13 +6899,13 @@
         <v>32368</v>
       </c>
       <c r="C385">
-        <v>42295</v>
+        <v>42303</v>
       </c>
       <c r="D385">
-        <v>60986</v>
+        <v>61548</v>
       </c>
       <c r="E385">
-        <v>80032</v>
+        <v>80575</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6919,10 +6919,10 @@
         <v>26287</v>
       </c>
       <c r="D386">
-        <v>45336</v>
+        <v>45485</v>
       </c>
       <c r="E386">
-        <v>65356</v>
+        <v>65626</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6936,10 +6936,10 @@
         <v>26287</v>
       </c>
       <c r="D387">
-        <v>45336</v>
+        <v>45485</v>
       </c>
       <c r="E387">
-        <v>65356</v>
+        <v>65626</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6950,13 +6950,13 @@
         <v>6094</v>
       </c>
       <c r="C388">
-        <v>9288</v>
+        <v>9289</v>
       </c>
       <c r="D388">
-        <v>23566</v>
+        <v>23568</v>
       </c>
       <c r="E388">
-        <v>41288</v>
+        <v>41316</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -6970,10 +6970,10 @@
         <v>8666</v>
       </c>
       <c r="D389">
-        <v>24968</v>
+        <v>24973</v>
       </c>
       <c r="E389">
-        <v>45143</v>
+        <v>45190</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6987,10 +6987,10 @@
         <v>8666</v>
       </c>
       <c r="D390">
-        <v>24968</v>
+        <v>24973</v>
       </c>
       <c r="E390">
-        <v>45143</v>
+        <v>45190</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7001,13 +7001,13 @@
         <v>6094</v>
       </c>
       <c r="C391">
-        <v>9288</v>
+        <v>9289</v>
       </c>
       <c r="D391">
-        <v>23566</v>
+        <v>23568</v>
       </c>
       <c r="E391">
-        <v>41288</v>
+        <v>41316</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7021,10 +7021,10 @@
         <v>8666</v>
       </c>
       <c r="D392">
-        <v>24968</v>
+        <v>24973</v>
       </c>
       <c r="E392">
-        <v>45143</v>
+        <v>45190</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7038,10 +7038,10 @@
         <v>7281</v>
       </c>
       <c r="D393">
-        <v>19056</v>
+        <v>19058</v>
       </c>
       <c r="E393">
-        <v>32845</v>
+        <v>32857</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7055,10 +7055,10 @@
         <v>7281</v>
       </c>
       <c r="D394">
-        <v>19056</v>
+        <v>19058</v>
       </c>
       <c r="E394">
-        <v>32845</v>
+        <v>32857</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7072,10 +7072,10 @@
         <v>8161</v>
       </c>
       <c r="D395">
-        <v>20375</v>
+        <v>20378</v>
       </c>
       <c r="E395">
-        <v>34755</v>
+        <v>34771</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7089,10 +7089,10 @@
         <v>8161</v>
       </c>
       <c r="D396">
-        <v>20375</v>
+        <v>20378</v>
       </c>
       <c r="E396">
-        <v>34755</v>
+        <v>34771</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7106,10 +7106,10 @@
         <v>8989</v>
       </c>
       <c r="D397">
-        <v>21525</v>
+        <v>21528</v>
       </c>
       <c r="E397">
-        <v>36891</v>
+        <v>36917</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7123,10 +7123,10 @@
         <v>8989</v>
       </c>
       <c r="D398">
-        <v>21525</v>
+        <v>21528</v>
       </c>
       <c r="E398">
-        <v>36891</v>
+        <v>36917</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,10 +7140,10 @@
         <v>8072</v>
       </c>
       <c r="D399">
-        <v>25841</v>
+        <v>25857</v>
       </c>
       <c r="E399">
-        <v>47950</v>
+        <v>48073</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7157,10 +7157,10 @@
         <v>7695</v>
       </c>
       <c r="D400">
-        <v>25541</v>
+        <v>25556</v>
       </c>
       <c r="E400">
-        <v>47851</v>
+        <v>47966</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>8072</v>
       </c>
       <c r="D401">
-        <v>25841</v>
+        <v>25857</v>
       </c>
       <c r="E401">
-        <v>47950</v>
+        <v>48073</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7191,10 +7191,10 @@
         <v>7497</v>
       </c>
       <c r="D402">
-        <v>23767</v>
+        <v>23774</v>
       </c>
       <c r="E402">
-        <v>44137</v>
+        <v>44222</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>7695</v>
       </c>
       <c r="D403">
-        <v>25541</v>
+        <v>25556</v>
       </c>
       <c r="E403">
-        <v>47851</v>
+        <v>47966</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7225,10 +7225,10 @@
         <v>6599</v>
       </c>
       <c r="D404">
-        <v>22931</v>
+        <v>22939</v>
       </c>
       <c r="E404">
-        <v>43240</v>
+        <v>43310</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7242,10 +7242,10 @@
         <v>6599</v>
       </c>
       <c r="D405">
-        <v>22931</v>
+        <v>22939</v>
       </c>
       <c r="E405">
-        <v>43240</v>
+        <v>43310</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7259,10 +7259,10 @@
         <v>6599</v>
       </c>
       <c r="D406">
-        <v>22931</v>
+        <v>22939</v>
       </c>
       <c r="E406">
-        <v>43240</v>
+        <v>43310</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7276,10 +7276,10 @@
         <v>5778</v>
       </c>
       <c r="D407">
-        <v>21233</v>
+        <v>21238</v>
       </c>
       <c r="E407">
-        <v>40401</v>
+        <v>40450</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7293,10 +7293,10 @@
         <v>5778</v>
       </c>
       <c r="D408">
-        <v>21233</v>
+        <v>21238</v>
       </c>
       <c r="E408">
-        <v>40401</v>
+        <v>40450</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7310,10 +7310,10 @@
         <v>5778</v>
       </c>
       <c r="D409">
-        <v>21233</v>
+        <v>21238</v>
       </c>
       <c r="E409">
-        <v>40401</v>
+        <v>40450</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7321,16 +7321,16 @@
         <v>409</v>
       </c>
       <c r="B410">
-        <v>9425</v>
+        <v>9426</v>
       </c>
       <c r="C410">
-        <v>16948</v>
+        <v>16980</v>
       </c>
       <c r="D410">
-        <v>41197</v>
+        <v>41487</v>
       </c>
       <c r="E410">
-        <v>68105</v>
+        <v>68663</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7341,13 +7341,13 @@
         <v>7571</v>
       </c>
       <c r="C411">
-        <v>13513</v>
+        <v>13518</v>
       </c>
       <c r="D411">
-        <v>35464</v>
+        <v>35567</v>
       </c>
       <c r="E411">
-        <v>61254</v>
+        <v>61611</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7358,13 +7358,13 @@
         <v>7571</v>
       </c>
       <c r="C412">
-        <v>13513</v>
+        <v>13518</v>
       </c>
       <c r="D412">
-        <v>35464</v>
+        <v>35567</v>
       </c>
       <c r="E412">
-        <v>61254</v>
+        <v>61611</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7375,13 +7375,13 @@
         <v>7719</v>
       </c>
       <c r="C413">
-        <v>13827</v>
+        <v>13834</v>
       </c>
       <c r="D413">
-        <v>35591</v>
+        <v>35698</v>
       </c>
       <c r="E413">
-        <v>60438</v>
+        <v>60784</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7389,16 +7389,16 @@
         <v>413</v>
       </c>
       <c r="B414">
-        <v>9425</v>
+        <v>9426</v>
       </c>
       <c r="C414">
-        <v>16948</v>
+        <v>16980</v>
       </c>
       <c r="D414">
-        <v>41197</v>
+        <v>41487</v>
       </c>
       <c r="E414">
-        <v>68105</v>
+        <v>68663</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7409,13 +7409,13 @@
         <v>8025</v>
       </c>
       <c r="C415">
-        <v>14347</v>
+        <v>14358</v>
       </c>
       <c r="D415">
-        <v>37516</v>
+        <v>37694</v>
       </c>
       <c r="E415">
-        <v>64335</v>
+        <v>64805</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7426,13 +7426,13 @@
         <v>8025</v>
       </c>
       <c r="C416">
-        <v>14347</v>
+        <v>14358</v>
       </c>
       <c r="D416">
-        <v>37516</v>
+        <v>37694</v>
       </c>
       <c r="E416">
-        <v>64335</v>
+        <v>64805</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7443,13 +7443,13 @@
         <v>6273</v>
       </c>
       <c r="C417">
-        <v>10664</v>
+        <v>10667</v>
       </c>
       <c r="D417">
-        <v>30548</v>
+        <v>30604</v>
       </c>
       <c r="E417">
-        <v>54896</v>
+        <v>55158</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7460,13 +7460,13 @@
         <v>6273</v>
       </c>
       <c r="C418">
-        <v>10664</v>
+        <v>10667</v>
       </c>
       <c r="D418">
-        <v>30548</v>
+        <v>30604</v>
       </c>
       <c r="E418">
-        <v>54896</v>
+        <v>55158</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,10 +7480,10 @@
         <v>16372</v>
       </c>
       <c r="D419">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E419">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7497,10 +7497,10 @@
         <v>16372</v>
       </c>
       <c r="D420">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E420">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7514,10 +7514,10 @@
         <v>15907</v>
       </c>
       <c r="D421">
-        <v>33615</v>
+        <v>33662</v>
       </c>
       <c r="E421">
-        <v>55095</v>
+        <v>55281</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>15907</v>
       </c>
       <c r="D422">
-        <v>33615</v>
+        <v>33662</v>
       </c>
       <c r="E422">
-        <v>55095</v>
+        <v>55281</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,10 +7548,10 @@
         <v>16372</v>
       </c>
       <c r="D423">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E423">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7565,10 +7565,10 @@
         <v>16372</v>
       </c>
       <c r="D424">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E424">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7582,10 +7582,10 @@
         <v>15907</v>
       </c>
       <c r="D425">
-        <v>33615</v>
+        <v>33662</v>
       </c>
       <c r="E425">
-        <v>55095</v>
+        <v>55281</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,10 +7599,10 @@
         <v>16372</v>
       </c>
       <c r="D426">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E426">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7616,10 +7616,10 @@
         <v>16372</v>
       </c>
       <c r="D427">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E427">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>16372</v>
       </c>
       <c r="D428">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E428">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,10 +7650,10 @@
         <v>16372</v>
       </c>
       <c r="D429">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E429">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7667,10 +7667,10 @@
         <v>16372</v>
       </c>
       <c r="D430">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E430">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7684,10 +7684,10 @@
         <v>15907</v>
       </c>
       <c r="D431">
-        <v>33615</v>
+        <v>33662</v>
       </c>
       <c r="E431">
-        <v>55095</v>
+        <v>55281</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,10 +7701,10 @@
         <v>16372</v>
       </c>
       <c r="D432">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E432">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -7718,10 +7718,10 @@
         <v>16372</v>
       </c>
       <c r="D433">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E433">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7735,10 +7735,10 @@
         <v>12309</v>
       </c>
       <c r="D434">
-        <v>28090</v>
+        <v>28108</v>
       </c>
       <c r="E434">
-        <v>47149</v>
+        <v>47226</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7752,10 +7752,10 @@
         <v>16372</v>
       </c>
       <c r="D435">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E435">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7769,10 +7769,10 @@
         <v>11618</v>
       </c>
       <c r="D436">
-        <v>28276</v>
+        <v>28291</v>
       </c>
       <c r="E436">
-        <v>47911</v>
+        <v>48004</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>9223</v>
       </c>
       <c r="D437">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E437">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>9223</v>
       </c>
       <c r="D438">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E438">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>9223</v>
       </c>
       <c r="D439">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E439">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>9223</v>
       </c>
       <c r="D440">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E440">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>9223</v>
       </c>
       <c r="D441">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E441">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>9223</v>
       </c>
       <c r="D442">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E442">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>9223</v>
       </c>
       <c r="D443">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E443">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>9223</v>
       </c>
       <c r="D444">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E444">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>9223</v>
       </c>
       <c r="D445">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E445">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>9223</v>
       </c>
       <c r="D446">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E446">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>9223</v>
       </c>
       <c r="D447">
-        <v>23155</v>
+        <v>23160</v>
       </c>
       <c r="E447">
-        <v>39322</v>
+        <v>39354</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>24433</v>
       </c>
       <c r="D448">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E448">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>24433</v>
       </c>
       <c r="D449">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E449">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>24433</v>
       </c>
       <c r="D450">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E450">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>24433</v>
       </c>
       <c r="D451">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E451">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>24433</v>
       </c>
       <c r="D452">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E452">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>24433</v>
       </c>
       <c r="D453">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E453">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8072,13 +8072,13 @@
         <v>14391</v>
       </c>
       <c r="C454">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D454">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E454">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8089,13 +8089,13 @@
         <v>14391</v>
       </c>
       <c r="C455">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D455">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E455">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8106,13 +8106,13 @@
         <v>14391</v>
       </c>
       <c r="C456">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D456">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E456">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8123,13 +8123,13 @@
         <v>14391</v>
       </c>
       <c r="C457">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D457">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E457">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8140,13 +8140,13 @@
         <v>14391</v>
       </c>
       <c r="C458">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D458">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E458">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8157,13 +8157,13 @@
         <v>14391</v>
       </c>
       <c r="C459">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D459">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E459">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8174,13 +8174,13 @@
         <v>14391</v>
       </c>
       <c r="C460">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D460">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E460">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8191,13 +8191,13 @@
         <v>14391</v>
       </c>
       <c r="C461">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D461">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E461">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8208,13 +8208,13 @@
         <v>14391</v>
       </c>
       <c r="C462">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D462">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E462">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>16372</v>
       </c>
       <c r="D463">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E463">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>16372</v>
       </c>
       <c r="D464">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E464">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8262,10 +8262,10 @@
         <v>12309</v>
       </c>
       <c r="D465">
-        <v>28090</v>
+        <v>28108</v>
       </c>
       <c r="E465">
-        <v>47149</v>
+        <v>47226</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -8279,10 +8279,10 @@
         <v>12309</v>
       </c>
       <c r="D466">
-        <v>28090</v>
+        <v>28108</v>
       </c>
       <c r="E466">
-        <v>47149</v>
+        <v>47226</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>16372</v>
       </c>
       <c r="D467">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E467">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>24433</v>
       </c>
       <c r="D468">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E468">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>24433</v>
       </c>
       <c r="D469">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E469">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>24433</v>
       </c>
       <c r="D470">
-        <v>42162</v>
+        <v>42174</v>
       </c>
       <c r="E470">
-        <v>64213</v>
+        <v>64431</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>16372</v>
       </c>
       <c r="D471">
-        <v>34711</v>
+        <v>34754</v>
       </c>
       <c r="E471">
-        <v>56849</v>
+        <v>57027</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8378,13 +8378,13 @@
         <v>14391</v>
       </c>
       <c r="C472">
-        <v>19243</v>
+        <v>19247</v>
       </c>
       <c r="D472">
-        <v>37754</v>
+        <v>37782</v>
       </c>
       <c r="E472">
-        <v>60160</v>
+        <v>60334</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>12309</v>
       </c>
       <c r="D473">
-        <v>28090</v>
+        <v>28108</v>
       </c>
       <c r="E473">
-        <v>47149</v>
+        <v>47226</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>12309</v>
       </c>
       <c r="D474">
-        <v>28090</v>
+        <v>28108</v>
       </c>
       <c r="E474">
-        <v>47149</v>
+        <v>47226</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>11618</v>
       </c>
       <c r="D475">
-        <v>28276</v>
+        <v>28291</v>
       </c>
       <c r="E475">
-        <v>47911</v>
+        <v>48004</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>11460</v>
       </c>
       <c r="D476">
-        <v>27642</v>
+        <v>27657</v>
       </c>
       <c r="E476">
-        <v>46711</v>
+        <v>46770</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>11460</v>
       </c>
       <c r="D477">
-        <v>27642</v>
+        <v>27657</v>
       </c>
       <c r="E477">
-        <v>46711</v>
+        <v>46770</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8480,13 +8480,13 @@
         <v>8508</v>
       </c>
       <c r="C478">
-        <v>12938</v>
+        <v>12940</v>
       </c>
       <c r="D478">
-        <v>30583</v>
+        <v>30611</v>
       </c>
       <c r="E478">
-        <v>52156</v>
+        <v>52321</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8500,10 +8500,10 @@
         <v>11681</v>
       </c>
       <c r="D479">
-        <v>28712</v>
+        <v>28729</v>
       </c>
       <c r="E479">
-        <v>49628</v>
+        <v>49729</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8514,13 +8514,13 @@
         <v>8651</v>
       </c>
       <c r="C480">
-        <v>13327</v>
+        <v>13329</v>
       </c>
       <c r="D480">
-        <v>31627</v>
+        <v>31653</v>
       </c>
       <c r="E480">
-        <v>53909</v>
+        <v>54067</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -8531,13 +8531,13 @@
         <v>8508</v>
       </c>
       <c r="C481">
-        <v>12938</v>
+        <v>12940</v>
       </c>
       <c r="D481">
-        <v>30583</v>
+        <v>30611</v>
       </c>
       <c r="E481">
-        <v>52156</v>
+        <v>52321</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8548,13 +8548,13 @@
         <v>8508</v>
       </c>
       <c r="C482">
-        <v>12938</v>
+        <v>12940</v>
       </c>
       <c r="D482">
-        <v>30583</v>
+        <v>30611</v>
       </c>
       <c r="E482">
-        <v>52156</v>
+        <v>52321</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8565,13 +8565,13 @@
         <v>8508</v>
       </c>
       <c r="C483">
-        <v>12938</v>
+        <v>12940</v>
       </c>
       <c r="D483">
-        <v>30583</v>
+        <v>30611</v>
       </c>
       <c r="E483">
-        <v>52156</v>
+        <v>52321</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8582,13 +8582,13 @@
         <v>8508</v>
       </c>
       <c r="C484">
-        <v>12938</v>
+        <v>12940</v>
       </c>
       <c r="D484">
-        <v>30583</v>
+        <v>30611</v>
       </c>
       <c r="E484">
-        <v>52156</v>
+        <v>52321</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8599,13 +8599,13 @@
         <v>8651</v>
       </c>
       <c r="C485">
-        <v>13327</v>
+        <v>13329</v>
       </c>
       <c r="D485">
-        <v>31627</v>
+        <v>31653</v>
       </c>
       <c r="E485">
-        <v>53909</v>
+        <v>54067</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -8616,13 +8616,13 @@
         <v>8156</v>
       </c>
       <c r="C486">
-        <v>12729</v>
+        <v>12730</v>
       </c>
       <c r="D486">
-        <v>30711</v>
+        <v>30734</v>
       </c>
       <c r="E486">
-        <v>52709</v>
+        <v>52843</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -8636,10 +8636,10 @@
         <v>12064</v>
       </c>
       <c r="D487">
-        <v>28494</v>
+        <v>28506</v>
       </c>
       <c r="E487">
-        <v>48608</v>
+        <v>48694</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8650,13 +8650,13 @@
         <v>8504</v>
       </c>
       <c r="C488">
-        <v>12785</v>
+        <v>12786</v>
       </c>
       <c r="D488">
-        <v>29449</v>
+        <v>29463</v>
       </c>
       <c r="E488">
-        <v>49658</v>
+        <v>49731</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8667,13 +8667,13 @@
         <v>8504</v>
       </c>
       <c r="C489">
-        <v>12785</v>
+        <v>12786</v>
       </c>
       <c r="D489">
-        <v>29449</v>
+        <v>29463</v>
       </c>
       <c r="E489">
-        <v>49658</v>
+        <v>49731</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8684,13 +8684,13 @@
         <v>11523</v>
       </c>
       <c r="C490">
-        <v>17921</v>
+        <v>17925</v>
       </c>
       <c r="D490">
-        <v>39361</v>
+        <v>39459</v>
       </c>
       <c r="E490">
-        <v>64260</v>
+        <v>64626</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -8701,13 +8701,13 @@
         <v>11523</v>
       </c>
       <c r="C491">
-        <v>17921</v>
+        <v>17925</v>
       </c>
       <c r="D491">
-        <v>39361</v>
+        <v>39459</v>
       </c>
       <c r="E491">
-        <v>64260</v>
+        <v>64626</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8718,13 +8718,13 @@
         <v>11523</v>
       </c>
       <c r="C492">
-        <v>17921</v>
+        <v>17925</v>
       </c>
       <c r="D492">
-        <v>39361</v>
+        <v>39459</v>
       </c>
       <c r="E492">
-        <v>64260</v>
+        <v>64626</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8735,13 +8735,13 @@
         <v>11523</v>
       </c>
       <c r="C493">
-        <v>17921</v>
+        <v>17925</v>
       </c>
       <c r="D493">
-        <v>39361</v>
+        <v>39459</v>
       </c>
       <c r="E493">
-        <v>64260</v>
+        <v>64626</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8752,13 +8752,13 @@
         <v>11523</v>
       </c>
       <c r="C494">
-        <v>17921</v>
+        <v>17925</v>
       </c>
       <c r="D494">
-        <v>39361</v>
+        <v>39459</v>
       </c>
       <c r="E494">
-        <v>64260</v>
+        <v>64626</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -8769,13 +8769,13 @@
         <v>10403</v>
       </c>
       <c r="C495">
-        <v>18019</v>
+        <v>18033</v>
       </c>
       <c r="D495">
-        <v>40974</v>
+        <v>41146</v>
       </c>
       <c r="E495">
-        <v>66568</v>
+        <v>67014</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,13 +8786,13 @@
         <v>11992</v>
       </c>
       <c r="C496">
-        <v>19855</v>
+        <v>19871</v>
       </c>
       <c r="D496">
-        <v>43060</v>
+        <v>43270</v>
       </c>
       <c r="E496">
-        <v>68731</v>
+        <v>69229</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>10403</v>
       </c>
       <c r="C497">
-        <v>18019</v>
+        <v>18033</v>
       </c>
       <c r="D497">
-        <v>40974</v>
+        <v>41146</v>
       </c>
       <c r="E497">
-        <v>66568</v>
+        <v>67014</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8820,13 +8820,13 @@
         <v>13841</v>
       </c>
       <c r="C498">
-        <v>20143</v>
+        <v>20145</v>
       </c>
       <c r="D498">
-        <v>39939</v>
+        <v>40075</v>
       </c>
       <c r="E498">
-        <v>62878</v>
+        <v>63255</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8837,13 +8837,13 @@
         <v>13841</v>
       </c>
       <c r="C499">
-        <v>20143</v>
+        <v>20145</v>
       </c>
       <c r="D499">
-        <v>39939</v>
+        <v>40075</v>
       </c>
       <c r="E499">
-        <v>62878</v>
+        <v>63255</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8854,13 +8854,13 @@
         <v>13841</v>
       </c>
       <c r="C500">
-        <v>20143</v>
+        <v>20145</v>
       </c>
       <c r="D500">
-        <v>39939</v>
+        <v>40075</v>
       </c>
       <c r="E500">
-        <v>62878</v>
+        <v>63255</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>14483</v>
       </c>
       <c r="D501">
-        <v>31117</v>
+        <v>31136</v>
       </c>
       <c r="E501">
-        <v>51530</v>
+        <v>51620</v>
       </c>
     </row>
   </sheetData>
